--- a/source/8、绩效异常岗位/2、卸车岗/卸车岗-6月.xlsx
+++ b/source/8、绩效异常岗位/2、卸车岗/卸车岗-6月.xlsx
@@ -11,6 +11,9 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$65</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
@@ -29,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="371" uniqueCount="61">
   <si>
     <t>数据日期</t>
   </si>
@@ -64,9 +67,6 @@
     <t>柳州</t>
   </si>
   <si>
-    <t>91.2</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -76,187 +76,145 @@
     <t>银川</t>
   </si>
   <si>
-    <t>111.5</t>
-  </si>
-  <si>
     <t>广东区</t>
   </si>
   <si>
     <t>东莞</t>
   </si>
   <si>
-    <t>151.8</t>
-  </si>
-  <si>
     <t>湖南区</t>
   </si>
   <si>
     <t>长沙</t>
   </si>
   <si>
-    <t>153.1</t>
-  </si>
-  <si>
     <t>河北区</t>
   </si>
   <si>
     <t>邢邯</t>
   </si>
   <si>
-    <t>136.5</t>
-  </si>
-  <si>
     <t>贵州区</t>
   </si>
   <si>
     <t>贵阳</t>
   </si>
   <si>
-    <t>184.1</t>
-  </si>
-  <si>
     <t>天津区</t>
   </si>
   <si>
     <t>天津</t>
   </si>
   <si>
-    <t>134.6</t>
-  </si>
-  <si>
     <t>浙北区</t>
   </si>
   <si>
     <t>宁波</t>
   </si>
   <si>
-    <t>141.3</t>
-  </si>
-  <si>
     <t>山西区</t>
   </si>
   <si>
     <t>太原</t>
   </si>
   <si>
-    <t>154.8</t>
-  </si>
-  <si>
     <t>浙南区</t>
   </si>
   <si>
     <t>义乌</t>
   </si>
   <si>
-    <t>207</t>
-  </si>
-  <si>
     <t>山东区</t>
   </si>
   <si>
     <t>潍坊</t>
   </si>
   <si>
-    <t>148.4</t>
-  </si>
-  <si>
     <t>内蒙古区</t>
   </si>
   <si>
     <t>呼和浩特</t>
   </si>
   <si>
-    <t>106.3</t>
-  </si>
-  <si>
     <t>黑龙江区</t>
   </si>
   <si>
     <t>哈尔滨</t>
   </si>
   <si>
-    <t>145</t>
-  </si>
-  <si>
     <t>湖北区</t>
   </si>
   <si>
     <t>武昌</t>
   </si>
   <si>
-    <t>118.4</t>
-  </si>
-  <si>
     <t>粤东区</t>
   </si>
   <si>
     <t>揭阳</t>
   </si>
   <si>
-    <t>216.6</t>
-  </si>
-  <si>
     <t>辽宁区</t>
   </si>
   <si>
     <t>盘锦</t>
   </si>
   <si>
-    <t>128.4</t>
-  </si>
-  <si>
     <t>武汉</t>
   </si>
   <si>
-    <t>141</t>
-  </si>
-  <si>
     <t>安徽区</t>
   </si>
   <si>
     <t>合肥</t>
   </si>
   <si>
-    <t>168.9</t>
-  </si>
-  <si>
     <t>芜湖</t>
   </si>
   <si>
-    <t>178.2</t>
-  </si>
-  <si>
     <t>江苏区</t>
   </si>
   <si>
     <t>南通</t>
   </si>
   <si>
-    <t>197.3</t>
-  </si>
-  <si>
     <t>淮安</t>
   </si>
   <si>
-    <t>209.5</t>
-  </si>
-  <si>
     <t>广州</t>
   </si>
   <si>
-    <t>180</t>
-  </si>
-  <si>
     <t>临沂</t>
   </si>
   <si>
-    <t>220.3</t>
-  </si>
-  <si>
     <t>杭州</t>
   </si>
   <si>
-    <t>220.1</t>
+    <t>2026-06-02</t>
+  </si>
+  <si>
+    <t>无锡</t>
+  </si>
+  <si>
+    <t>深圳</t>
+  </si>
+  <si>
+    <t>2026-06-03</t>
+  </si>
+  <si>
+    <t>2026-06-04</t>
+  </si>
+  <si>
+    <t>2026-06-05</t>
+  </si>
+  <si>
+    <t>长治</t>
+  </si>
+  <si>
+    <t>甘肃区</t>
+  </si>
+  <si>
+    <t>兰州</t>
   </si>
 </sst>
 </file>
@@ -1187,7 +1145,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H25"/>
+  <dimension ref="A1:H106"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <sheetData>
     <row r="1" spans="1:8">
@@ -1226,8 +1184,8 @@
       <c r="C2" t="s">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
-        <v>11</v>
+      <c r="D2">
+        <v>91.2</v>
       </c>
       <c r="E2">
         <v>142.9</v>
@@ -1236,10 +1194,10 @@
         <v>56.7</v>
       </c>
       <c r="G2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -1247,13 +1205,13 @@
         <v>8</v>
       </c>
       <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
         <v>13</v>
       </c>
-      <c r="C3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>15</v>
+      <c r="D3">
+        <v>111.5</v>
       </c>
       <c r="E3">
         <v>170.3</v>
@@ -1273,13 +1231,13 @@
         <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C4" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>18</v>
+        <v>15</v>
+      </c>
+      <c r="D4">
+        <v>151.8</v>
       </c>
       <c r="E4">
         <v>186.6</v>
@@ -1299,13 +1257,13 @@
         <v>8</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="C5" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" t="s">
-        <v>21</v>
+        <v>17</v>
+      </c>
+      <c r="D5">
+        <v>153.1</v>
       </c>
       <c r="E5">
         <v>185.9</v>
@@ -1325,13 +1283,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
+        <v>19</v>
+      </c>
+      <c r="D6">
+        <v>136.5</v>
       </c>
       <c r="E6">
         <v>164.4</v>
@@ -1351,13 +1309,13 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
-      </c>
-      <c r="D7" t="s">
-        <v>27</v>
+        <v>21</v>
+      </c>
+      <c r="D7">
+        <v>184.1</v>
       </c>
       <c r="E7">
         <v>216.4</v>
@@ -1377,13 +1335,13 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" t="s">
-        <v>30</v>
+        <v>23</v>
+      </c>
+      <c r="D8">
+        <v>134.6</v>
       </c>
       <c r="E8">
         <v>156.3</v>
@@ -1392,10 +1350,10 @@
         <v>16.1</v>
       </c>
       <c r="G8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H8" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8">
@@ -1403,13 +1361,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>32</v>
-      </c>
-      <c r="D9" t="s">
-        <v>33</v>
+        <v>25</v>
+      </c>
+      <c r="D9">
+        <v>141.3</v>
       </c>
       <c r="E9">
         <v>163.9</v>
@@ -1429,13 +1387,13 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
-      </c>
-      <c r="D10" t="s">
-        <v>36</v>
+        <v>27</v>
+      </c>
+      <c r="D10">
+        <v>154.8</v>
       </c>
       <c r="E10">
         <v>176.8</v>
@@ -1455,13 +1413,13 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
-      </c>
-      <c r="D11" t="s">
-        <v>39</v>
+        <v>29</v>
+      </c>
+      <c r="D11">
+        <v>207</v>
       </c>
       <c r="E11">
         <v>235.9</v>
@@ -1481,13 +1439,13 @@
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D12" t="s">
-        <v>42</v>
+        <v>31</v>
+      </c>
+      <c r="D12">
+        <v>148.4</v>
       </c>
       <c r="E12">
         <v>169</v>
@@ -1507,13 +1465,13 @@
         <v>8</v>
       </c>
       <c r="B13" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="C13" t="s">
-        <v>44</v>
-      </c>
-      <c r="D13" t="s">
-        <v>45</v>
+        <v>33</v>
+      </c>
+      <c r="D13">
+        <v>106.3</v>
       </c>
       <c r="E13">
         <v>121</v>
@@ -1522,10 +1480,10 @@
         <v>13.8</v>
       </c>
       <c r="G13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="14" spans="1:8">
@@ -1533,13 +1491,13 @@
         <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="C14" t="s">
-        <v>47</v>
-      </c>
-      <c r="D14" t="s">
-        <v>48</v>
+        <v>35</v>
+      </c>
+      <c r="D14">
+        <v>145</v>
       </c>
       <c r="E14">
         <v>164.6</v>
@@ -1559,13 +1517,13 @@
         <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D15" t="s">
-        <v>51</v>
+        <v>37</v>
+      </c>
+      <c r="D15">
+        <v>118.4</v>
       </c>
       <c r="E15">
         <v>133.2</v>
@@ -1574,10 +1532,10 @@
         <v>12.4</v>
       </c>
       <c r="G15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:8">
@@ -1585,13 +1543,13 @@
         <v>8</v>
       </c>
       <c r="B16" t="s">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="C16" t="s">
-        <v>53</v>
-      </c>
-      <c r="D16" t="s">
-        <v>54</v>
+        <v>39</v>
+      </c>
+      <c r="D16">
+        <v>216.6</v>
       </c>
       <c r="E16">
         <v>242.2</v>
@@ -1611,13 +1569,13 @@
         <v>8</v>
       </c>
       <c r="B17" t="s">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="C17" t="s">
-        <v>56</v>
-      </c>
-      <c r="D17" t="s">
-        <v>57</v>
+        <v>41</v>
+      </c>
+      <c r="D17">
+        <v>128.4</v>
       </c>
       <c r="E17">
         <v>143.1</v>
@@ -1626,10 +1584,10 @@
         <v>11.4</v>
       </c>
       <c r="G17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H17" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1637,13 +1595,13 @@
         <v>8</v>
       </c>
       <c r="B18" t="s">
-        <v>49</v>
+        <v>36</v>
       </c>
       <c r="C18" t="s">
-        <v>58</v>
-      </c>
-      <c r="D18" t="s">
-        <v>59</v>
+        <v>42</v>
+      </c>
+      <c r="D18">
+        <v>141</v>
       </c>
       <c r="E18">
         <v>157</v>
@@ -1652,10 +1610,10 @@
         <v>11.3</v>
       </c>
       <c r="G18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H18" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1663,13 +1621,13 @@
         <v>8</v>
       </c>
       <c r="B19" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C19" t="s">
-        <v>61</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
+        <v>44</v>
+      </c>
+      <c r="D19">
+        <v>168.9</v>
       </c>
       <c r="E19">
         <v>187.4</v>
@@ -1689,13 +1647,13 @@
         <v>8</v>
       </c>
       <c r="B20" t="s">
-        <v>60</v>
+        <v>43</v>
       </c>
       <c r="C20" t="s">
-        <v>63</v>
-      </c>
-      <c r="D20" t="s">
-        <v>64</v>
+        <v>45</v>
+      </c>
+      <c r="D20">
+        <v>178.2</v>
       </c>
       <c r="E20">
         <v>188.8</v>
@@ -1715,13 +1673,13 @@
         <v>8</v>
       </c>
       <c r="B21" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C21" t="s">
-        <v>66</v>
-      </c>
-      <c r="D21" t="s">
-        <v>67</v>
+        <v>47</v>
+      </c>
+      <c r="D21">
+        <v>197.3</v>
       </c>
       <c r="E21">
         <v>208.5</v>
@@ -1741,13 +1699,13 @@
         <v>8</v>
       </c>
       <c r="B22" t="s">
-        <v>65</v>
+        <v>46</v>
       </c>
       <c r="C22" t="s">
-        <v>68</v>
-      </c>
-      <c r="D22" t="s">
-        <v>69</v>
+        <v>48</v>
+      </c>
+      <c r="D22">
+        <v>209.5</v>
       </c>
       <c r="E22">
         <v>214.2</v>
@@ -1767,13 +1725,13 @@
         <v>8</v>
       </c>
       <c r="B23" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C23" t="s">
-        <v>70</v>
-      </c>
-      <c r="D23" t="s">
-        <v>71</v>
+        <v>49</v>
+      </c>
+      <c r="D23">
+        <v>180</v>
       </c>
       <c r="E23">
         <v>179.5</v>
@@ -1793,13 +1751,13 @@
         <v>8</v>
       </c>
       <c r="B24" t="s">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="C24" t="s">
-        <v>72</v>
-      </c>
-      <c r="D24" t="s">
-        <v>73</v>
+        <v>50</v>
+      </c>
+      <c r="D24">
+        <v>220.3</v>
       </c>
       <c r="E24">
         <v>214.9</v>
@@ -1819,13 +1777,13 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>75</v>
+        <v>51</v>
+      </c>
+      <c r="D25">
+        <v>220.1</v>
       </c>
       <c r="E25">
         <v>206</v>
@@ -1840,7 +1798,2116 @@
         <v>27.9</v>
       </c>
     </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>52</v>
+      </c>
+      <c r="B26" t="s">
+        <v>12</v>
+      </c>
+      <c r="C26" t="s">
+        <v>13</v>
+      </c>
+      <c r="D26">
+        <v>111.5</v>
+      </c>
+      <c r="E26">
+        <v>149.5</v>
+      </c>
+      <c r="F26">
+        <v>34</v>
+      </c>
+      <c r="G26" t="s">
+        <v>11</v>
+      </c>
+      <c r="H26" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>52</v>
+      </c>
+      <c r="B27" t="s">
+        <v>9</v>
+      </c>
+      <c r="C27" t="s">
+        <v>10</v>
+      </c>
+      <c r="D27">
+        <v>91.2</v>
+      </c>
+      <c r="E27">
+        <v>114</v>
+      </c>
+      <c r="F27">
+        <v>25</v>
+      </c>
+      <c r="G27" t="s">
+        <v>11</v>
+      </c>
+      <c r="H27" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>52</v>
+      </c>
+      <c r="B28" t="s">
+        <v>14</v>
+      </c>
+      <c r="C28" t="s">
+        <v>15</v>
+      </c>
+      <c r="D28">
+        <v>151.8</v>
+      </c>
+      <c r="E28">
+        <v>188.7</v>
+      </c>
+      <c r="F28">
+        <v>24.3</v>
+      </c>
+      <c r="G28">
+        <v>160.2</v>
+      </c>
+      <c r="H28">
+        <v>17.8</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>52</v>
+      </c>
+      <c r="B29" t="s">
+        <v>24</v>
+      </c>
+      <c r="C29" t="s">
+        <v>25</v>
+      </c>
+      <c r="D29">
+        <v>141.3</v>
+      </c>
+      <c r="E29">
+        <v>165.1</v>
+      </c>
+      <c r="F29">
+        <v>16.8</v>
+      </c>
+      <c r="G29">
+        <v>160.2</v>
+      </c>
+      <c r="H29">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="A30" t="s">
+        <v>52</v>
+      </c>
+      <c r="B30" t="s">
+        <v>16</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+      <c r="D30">
+        <v>150.5</v>
+      </c>
+      <c r="E30">
+        <v>174</v>
+      </c>
+      <c r="F30">
+        <v>15.5</v>
+      </c>
+      <c r="G30">
+        <v>160.2</v>
+      </c>
+      <c r="H30">
+        <v>8.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8">
+      <c r="A31" t="s">
+        <v>52</v>
+      </c>
+      <c r="B31" t="s">
+        <v>18</v>
+      </c>
+      <c r="C31" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31">
+        <v>136.5</v>
+      </c>
+      <c r="E31">
+        <v>156</v>
+      </c>
+      <c r="F31">
+        <v>14.2</v>
+      </c>
+      <c r="G31" t="s">
+        <v>11</v>
+      </c>
+      <c r="H31" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8">
+      <c r="A32" t="s">
+        <v>52</v>
+      </c>
+      <c r="B32" t="s">
+        <v>30</v>
+      </c>
+      <c r="C32" t="s">
+        <v>31</v>
+      </c>
+      <c r="D32">
+        <v>148.4</v>
+      </c>
+      <c r="E32">
+        <v>167.3</v>
+      </c>
+      <c r="F32">
+        <v>12.7</v>
+      </c>
+      <c r="G32">
+        <v>160.2</v>
+      </c>
+      <c r="H32">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8">
+      <c r="A33" t="s">
+        <v>52</v>
+      </c>
+      <c r="B33" t="s">
+        <v>36</v>
+      </c>
+      <c r="C33" t="s">
+        <v>37</v>
+      </c>
+      <c r="D33">
+        <v>118.4</v>
+      </c>
+      <c r="E33">
+        <v>132.5</v>
+      </c>
+      <c r="F33">
+        <v>11.9</v>
+      </c>
+      <c r="G33" t="s">
+        <v>11</v>
+      </c>
+      <c r="H33" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8">
+      <c r="A34" t="s">
+        <v>52</v>
+      </c>
+      <c r="B34" t="s">
+        <v>46</v>
+      </c>
+      <c r="C34" t="s">
+        <v>53</v>
+      </c>
+      <c r="D34">
+        <v>142</v>
+      </c>
+      <c r="E34">
+        <v>158.5</v>
+      </c>
+      <c r="F34">
+        <v>11.6</v>
+      </c>
+      <c r="G34" t="s">
+        <v>11</v>
+      </c>
+      <c r="H34" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8">
+      <c r="A35" t="s">
+        <v>52</v>
+      </c>
+      <c r="B35" t="s">
+        <v>20</v>
+      </c>
+      <c r="C35" t="s">
+        <v>21</v>
+      </c>
+      <c r="D35">
+        <v>184.1</v>
+      </c>
+      <c r="E35">
+        <v>205.3</v>
+      </c>
+      <c r="F35">
+        <v>11.5</v>
+      </c>
+      <c r="G35">
+        <v>160.2</v>
+      </c>
+      <c r="H35">
+        <v>28.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8">
+      <c r="A36" t="s">
+        <v>52</v>
+      </c>
+      <c r="B36" t="s">
+        <v>46</v>
+      </c>
+      <c r="C36" t="s">
+        <v>47</v>
+      </c>
+      <c r="D36">
+        <v>197.3</v>
+      </c>
+      <c r="E36">
+        <v>218.1</v>
+      </c>
+      <c r="F36">
+        <v>10.5</v>
+      </c>
+      <c r="G36">
+        <v>160.2</v>
+      </c>
+      <c r="H36">
+        <v>36.1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8">
+      <c r="A37" t="s">
+        <v>52</v>
+      </c>
+      <c r="B37" t="s">
+        <v>38</v>
+      </c>
+      <c r="C37" t="s">
+        <v>39</v>
+      </c>
+      <c r="D37">
+        <v>216.6</v>
+      </c>
+      <c r="E37">
+        <v>239.4</v>
+      </c>
+      <c r="F37">
+        <v>10.5</v>
+      </c>
+      <c r="G37">
+        <v>160.2</v>
+      </c>
+      <c r="H37">
+        <v>49.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8">
+      <c r="A38" t="s">
+        <v>52</v>
+      </c>
+      <c r="B38" t="s">
+        <v>43</v>
+      </c>
+      <c r="C38" t="s">
+        <v>44</v>
+      </c>
+      <c r="D38">
+        <v>168.9</v>
+      </c>
+      <c r="E38">
+        <v>183.7</v>
+      </c>
+      <c r="F38">
+        <v>8.7</v>
+      </c>
+      <c r="G38">
+        <v>160.2</v>
+      </c>
+      <c r="H38">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8">
+      <c r="A39" t="s">
+        <v>52</v>
+      </c>
+      <c r="B39" t="s">
+        <v>28</v>
+      </c>
+      <c r="C39" t="s">
+        <v>29</v>
+      </c>
+      <c r="D39">
+        <v>227.5</v>
+      </c>
+      <c r="E39">
+        <v>241.8</v>
+      </c>
+      <c r="F39">
+        <v>6.2</v>
+      </c>
+      <c r="G39">
+        <v>160.2</v>
+      </c>
+      <c r="H39">
+        <v>50.9</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8">
+      <c r="A40" t="s">
+        <v>52</v>
+      </c>
+      <c r="B40" t="s">
+        <v>43</v>
+      </c>
+      <c r="C40" t="s">
+        <v>45</v>
+      </c>
+      <c r="D40">
+        <v>178.2</v>
+      </c>
+      <c r="E40">
+        <v>185.9</v>
+      </c>
+      <c r="F40">
+        <v>4.3</v>
+      </c>
+      <c r="G40">
+        <v>160.2</v>
+      </c>
+      <c r="H40">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8">
+      <c r="A41" t="s">
+        <v>52</v>
+      </c>
+      <c r="B41" t="s">
+        <v>46</v>
+      </c>
+      <c r="C41" t="s">
+        <v>48</v>
+      </c>
+      <c r="D41">
+        <v>209.5</v>
+      </c>
+      <c r="E41">
+        <v>217.3</v>
+      </c>
+      <c r="F41">
+        <v>3.7</v>
+      </c>
+      <c r="G41">
+        <v>160.2</v>
+      </c>
+      <c r="H41">
+        <v>35.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8">
+      <c r="A42" t="s">
+        <v>52</v>
+      </c>
+      <c r="B42" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" t="s">
+        <v>54</v>
+      </c>
+      <c r="D42">
+        <v>173.6</v>
+      </c>
+      <c r="E42">
+        <v>176.3</v>
+      </c>
+      <c r="F42">
+        <v>1.5</v>
+      </c>
+      <c r="G42">
+        <v>160.2</v>
+      </c>
+      <c r="H42">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8">
+      <c r="A43" t="s">
+        <v>52</v>
+      </c>
+      <c r="B43" t="s">
+        <v>30</v>
+      </c>
+      <c r="C43" t="s">
+        <v>50</v>
+      </c>
+      <c r="D43">
+        <v>220.3</v>
+      </c>
+      <c r="E43">
+        <v>223.2</v>
+      </c>
+      <c r="F43">
+        <v>1.3</v>
+      </c>
+      <c r="G43">
+        <v>160.2</v>
+      </c>
+      <c r="H43">
+        <v>39.3</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
+      <c r="A44" t="s">
+        <v>52</v>
+      </c>
+      <c r="B44" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" t="s">
+        <v>49</v>
+      </c>
+      <c r="D44">
+        <v>180</v>
+      </c>
+      <c r="E44">
+        <v>181.6</v>
+      </c>
+      <c r="F44">
+        <v>0.8</v>
+      </c>
+      <c r="G44">
+        <v>160.2</v>
+      </c>
+      <c r="H44">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8">
+      <c r="A45" t="s">
+        <v>52</v>
+      </c>
+      <c r="B45" t="s">
+        <v>24</v>
+      </c>
+      <c r="C45" t="s">
+        <v>51</v>
+      </c>
+      <c r="D45">
+        <v>220.1</v>
+      </c>
+      <c r="E45">
+        <v>215.8</v>
+      </c>
+      <c r="F45">
+        <v>-1.9</v>
+      </c>
+      <c r="G45">
+        <v>160.2</v>
+      </c>
+      <c r="H45">
+        <v>34.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8">
+      <c r="A46" t="s">
+        <v>55</v>
+      </c>
+      <c r="B46" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46">
+        <v>151.8</v>
+      </c>
+      <c r="E46">
+        <v>196.9</v>
+      </c>
+      <c r="F46">
+        <v>29.7</v>
+      </c>
+      <c r="G46">
+        <v>161.1</v>
+      </c>
+      <c r="H46">
+        <v>22.2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8">
+      <c r="A47" t="s">
+        <v>55</v>
+      </c>
+      <c r="B47" t="s">
+        <v>12</v>
+      </c>
+      <c r="C47" t="s">
+        <v>13</v>
+      </c>
+      <c r="D47">
+        <v>111.5</v>
+      </c>
+      <c r="E47">
+        <v>144.1</v>
+      </c>
+      <c r="F47">
+        <v>29.2</v>
+      </c>
+      <c r="G47" t="s">
+        <v>11</v>
+      </c>
+      <c r="H47" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>55</v>
+      </c>
+      <c r="B48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C48" t="s">
+        <v>10</v>
+      </c>
+      <c r="D48">
+        <v>91.2</v>
+      </c>
+      <c r="E48">
+        <v>108.3</v>
+      </c>
+      <c r="F48">
+        <v>18.7</v>
+      </c>
+      <c r="G48" t="s">
+        <v>11</v>
+      </c>
+      <c r="H48" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" t="s">
+        <v>24</v>
+      </c>
+      <c r="C49" t="s">
+        <v>25</v>
+      </c>
+      <c r="D49">
+        <v>141.3</v>
+      </c>
+      <c r="E49">
+        <v>162.5</v>
+      </c>
+      <c r="F49">
+        <v>14.9</v>
+      </c>
+      <c r="G49">
+        <v>161.1</v>
+      </c>
+      <c r="H49">
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8">
+      <c r="A50" t="s">
+        <v>55</v>
+      </c>
+      <c r="B50" t="s">
+        <v>16</v>
+      </c>
+      <c r="C50" t="s">
+        <v>17</v>
+      </c>
+      <c r="D50">
+        <v>150.5</v>
+      </c>
+      <c r="E50">
+        <v>171.6</v>
+      </c>
+      <c r="F50">
+        <v>13.9</v>
+      </c>
+      <c r="G50">
+        <v>161.1</v>
+      </c>
+      <c r="H50">
+        <v>6.4</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8">
+      <c r="A51" t="s">
+        <v>55</v>
+      </c>
+      <c r="B51" t="s">
+        <v>46</v>
+      </c>
+      <c r="C51" t="s">
+        <v>53</v>
+      </c>
+      <c r="D51">
+        <v>142</v>
+      </c>
+      <c r="E51">
+        <v>161.6</v>
+      </c>
+      <c r="F51">
+        <v>13.8</v>
+      </c>
+      <c r="G51">
+        <v>161.1</v>
+      </c>
+      <c r="H51">
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8">
+      <c r="A52" t="s">
+        <v>55</v>
+      </c>
+      <c r="B52" t="s">
+        <v>46</v>
+      </c>
+      <c r="C52" t="s">
+        <v>47</v>
+      </c>
+      <c r="D52">
+        <v>197.3</v>
+      </c>
+      <c r="E52">
+        <v>223.4</v>
+      </c>
+      <c r="F52">
+        <v>13.2</v>
+      </c>
+      <c r="G52">
+        <v>161.1</v>
+      </c>
+      <c r="H52">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8">
+      <c r="A53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B53" t="s">
+        <v>36</v>
+      </c>
+      <c r="C53" t="s">
+        <v>37</v>
+      </c>
+      <c r="D53">
+        <v>118.4</v>
+      </c>
+      <c r="E53">
+        <v>133.7</v>
+      </c>
+      <c r="F53">
+        <v>12.8</v>
+      </c>
+      <c r="G53" t="s">
+        <v>11</v>
+      </c>
+      <c r="H53" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8">
+      <c r="A54" t="s">
+        <v>55</v>
+      </c>
+      <c r="B54" t="s">
+        <v>38</v>
+      </c>
+      <c r="C54" t="s">
+        <v>39</v>
+      </c>
+      <c r="D54">
+        <v>216.6</v>
+      </c>
+      <c r="E54">
+        <v>243.4</v>
+      </c>
+      <c r="F54">
+        <v>12.3</v>
+      </c>
+      <c r="G54">
+        <v>161.1</v>
+      </c>
+      <c r="H54">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8">
+      <c r="A55" t="s">
+        <v>55</v>
+      </c>
+      <c r="B55" t="s">
+        <v>30</v>
+      </c>
+      <c r="C55" t="s">
+        <v>31</v>
+      </c>
+      <c r="D55">
+        <v>148.4</v>
+      </c>
+      <c r="E55">
+        <v>165.6</v>
+      </c>
+      <c r="F55">
+        <v>11.5</v>
+      </c>
+      <c r="G55">
+        <v>161.1</v>
+      </c>
+      <c r="H55">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8">
+      <c r="A56" t="s">
+        <v>55</v>
+      </c>
+      <c r="B56" t="s">
+        <v>18</v>
+      </c>
+      <c r="C56" t="s">
+        <v>19</v>
+      </c>
+      <c r="D56">
+        <v>136.5</v>
+      </c>
+      <c r="E56">
+        <v>152</v>
+      </c>
+      <c r="F56">
+        <v>11.3</v>
+      </c>
+      <c r="G56" t="s">
+        <v>11</v>
+      </c>
+      <c r="H56" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8">
+      <c r="A57" t="s">
+        <v>55</v>
+      </c>
+      <c r="B57" t="s">
+        <v>43</v>
+      </c>
+      <c r="C57" t="s">
+        <v>44</v>
+      </c>
+      <c r="D57">
+        <v>168.9</v>
+      </c>
+      <c r="E57">
+        <v>184.9</v>
+      </c>
+      <c r="F57">
+        <v>9.4</v>
+      </c>
+      <c r="G57">
+        <v>161.1</v>
+      </c>
+      <c r="H57">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8">
+      <c r="A58" t="s">
+        <v>55</v>
+      </c>
+      <c r="B58" t="s">
+        <v>20</v>
+      </c>
+      <c r="C58" t="s">
+        <v>21</v>
+      </c>
+      <c r="D58">
+        <v>184.1</v>
+      </c>
+      <c r="E58">
+        <v>199.6</v>
+      </c>
+      <c r="F58">
+        <v>8.4</v>
+      </c>
+      <c r="G58">
+        <v>161.1</v>
+      </c>
+      <c r="H58">
+        <v>23.8</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8">
+      <c r="A59" t="s">
+        <v>55</v>
+      </c>
+      <c r="B59" t="s">
+        <v>28</v>
+      </c>
+      <c r="C59" t="s">
+        <v>29</v>
+      </c>
+      <c r="D59">
+        <v>227.5</v>
+      </c>
+      <c r="E59">
+        <v>246</v>
+      </c>
+      <c r="F59">
+        <v>8.1</v>
+      </c>
+      <c r="G59">
+        <v>161.1</v>
+      </c>
+      <c r="H59">
+        <v>52.6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8">
+      <c r="A60" t="s">
+        <v>55</v>
+      </c>
+      <c r="B60" t="s">
+        <v>43</v>
+      </c>
+      <c r="C60" t="s">
+        <v>45</v>
+      </c>
+      <c r="D60">
+        <v>178.2</v>
+      </c>
+      <c r="E60">
+        <v>186.9</v>
+      </c>
+      <c r="F60">
+        <v>4.8</v>
+      </c>
+      <c r="G60">
+        <v>161.1</v>
+      </c>
+      <c r="H60">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8">
+      <c r="A61" t="s">
+        <v>55</v>
+      </c>
+      <c r="B61" t="s">
+        <v>46</v>
+      </c>
+      <c r="C61" t="s">
+        <v>48</v>
+      </c>
+      <c r="D61">
+        <v>209.5</v>
+      </c>
+      <c r="E61">
+        <v>215.9</v>
+      </c>
+      <c r="F61">
+        <v>3</v>
+      </c>
+      <c r="G61">
+        <v>161.1</v>
+      </c>
+      <c r="H61">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8">
+      <c r="A62" t="s">
+        <v>55</v>
+      </c>
+      <c r="B62" t="s">
+        <v>30</v>
+      </c>
+      <c r="C62" t="s">
+        <v>50</v>
+      </c>
+      <c r="D62">
+        <v>220.3</v>
+      </c>
+      <c r="E62">
+        <v>226.4</v>
+      </c>
+      <c r="F62">
+        <v>2.7</v>
+      </c>
+      <c r="G62">
+        <v>161.1</v>
+      </c>
+      <c r="H62">
+        <v>40.4</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8">
+      <c r="A63" t="s">
+        <v>55</v>
+      </c>
+      <c r="B63" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" t="s">
+        <v>54</v>
+      </c>
+      <c r="D63">
+        <v>173.6</v>
+      </c>
+      <c r="E63">
+        <v>178.5</v>
+      </c>
+      <c r="F63">
+        <v>2.7</v>
+      </c>
+      <c r="G63">
+        <v>161.1</v>
+      </c>
+      <c r="H63">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8">
+      <c r="A64" t="s">
+        <v>55</v>
+      </c>
+      <c r="B64" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" t="s">
+        <v>49</v>
+      </c>
+      <c r="D64">
+        <v>180</v>
+      </c>
+      <c r="E64">
+        <v>182.7</v>
+      </c>
+      <c r="F64">
+        <v>1.5</v>
+      </c>
+      <c r="G64">
+        <v>161.1</v>
+      </c>
+      <c r="H64">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8">
+      <c r="A65" t="s">
+        <v>55</v>
+      </c>
+      <c r="B65" t="s">
+        <v>24</v>
+      </c>
+      <c r="C65" t="s">
+        <v>51</v>
+      </c>
+      <c r="D65">
+        <v>220.1</v>
+      </c>
+      <c r="E65">
+        <v>215</v>
+      </c>
+      <c r="F65">
+        <v>-2.3</v>
+      </c>
+      <c r="G65">
+        <v>161.1</v>
+      </c>
+      <c r="H65">
+        <v>33.4</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8">
+      <c r="A66" t="s">
+        <v>56</v>
+      </c>
+      <c r="B66" t="s">
+        <v>14</v>
+      </c>
+      <c r="C66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66">
+        <v>151.8</v>
+      </c>
+      <c r="E66">
+        <v>200</v>
+      </c>
+      <c r="F66">
+        <v>31.7</v>
+      </c>
+      <c r="G66">
+        <v>161.6</v>
+      </c>
+      <c r="H66">
+        <v>23.7</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8">
+      <c r="A67" t="s">
+        <v>56</v>
+      </c>
+      <c r="B67" t="s">
+        <v>12</v>
+      </c>
+      <c r="C67" t="s">
+        <v>13</v>
+      </c>
+      <c r="D67">
+        <v>111.5</v>
+      </c>
+      <c r="E67">
+        <v>143</v>
+      </c>
+      <c r="F67">
+        <v>28.2</v>
+      </c>
+      <c r="G67" t="s">
+        <v>11</v>
+      </c>
+      <c r="H67" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8">
+      <c r="A68" t="s">
+        <v>56</v>
+      </c>
+      <c r="B68" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" t="s">
+        <v>10</v>
+      </c>
+      <c r="D68">
+        <v>91.2</v>
+      </c>
+      <c r="E68">
+        <v>106.3</v>
+      </c>
+      <c r="F68">
+        <v>16.5</v>
+      </c>
+      <c r="G68" t="s">
+        <v>11</v>
+      </c>
+      <c r="H68" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8">
+      <c r="A69" t="s">
+        <v>56</v>
+      </c>
+      <c r="B69" t="s">
+        <v>24</v>
+      </c>
+      <c r="C69" t="s">
+        <v>25</v>
+      </c>
+      <c r="D69">
+        <v>141.3</v>
+      </c>
+      <c r="E69">
+        <v>164.2</v>
+      </c>
+      <c r="F69">
+        <v>16.1</v>
+      </c>
+      <c r="G69">
+        <v>161.6</v>
+      </c>
+      <c r="H69">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8">
+      <c r="A70" t="s">
+        <v>56</v>
+      </c>
+      <c r="B70" t="s">
+        <v>46</v>
+      </c>
+      <c r="C70" t="s">
+        <v>53</v>
+      </c>
+      <c r="D70">
+        <v>142</v>
+      </c>
+      <c r="E70">
+        <v>162.3</v>
+      </c>
+      <c r="F70">
+        <v>14.3</v>
+      </c>
+      <c r="G70">
+        <v>161.6</v>
+      </c>
+      <c r="H70">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8">
+      <c r="A71" t="s">
+        <v>56</v>
+      </c>
+      <c r="B71" t="s">
+        <v>46</v>
+      </c>
+      <c r="C71" t="s">
+        <v>47</v>
+      </c>
+      <c r="D71">
+        <v>197.3</v>
+      </c>
+      <c r="E71">
+        <v>224.6</v>
+      </c>
+      <c r="F71">
+        <v>13.8</v>
+      </c>
+      <c r="G71">
+        <v>161.6</v>
+      </c>
+      <c r="H71">
+        <v>38.9</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8">
+      <c r="A72" t="s">
+        <v>56</v>
+      </c>
+      <c r="B72" t="s">
+        <v>36</v>
+      </c>
+      <c r="C72" t="s">
+        <v>37</v>
+      </c>
+      <c r="D72">
+        <v>118.4</v>
+      </c>
+      <c r="E72">
+        <v>133</v>
+      </c>
+      <c r="F72">
+        <v>12.3</v>
+      </c>
+      <c r="G72" t="s">
+        <v>11</v>
+      </c>
+      <c r="H72" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8">
+      <c r="A73" t="s">
+        <v>56</v>
+      </c>
+      <c r="B73" t="s">
+        <v>16</v>
+      </c>
+      <c r="C73" t="s">
+        <v>17</v>
+      </c>
+      <c r="D73">
+        <v>150.5</v>
+      </c>
+      <c r="E73">
+        <v>168.5</v>
+      </c>
+      <c r="F73">
+        <v>11.9</v>
+      </c>
+      <c r="G73">
+        <v>161.6</v>
+      </c>
+      <c r="H73">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8">
+      <c r="A74" t="s">
+        <v>56</v>
+      </c>
+      <c r="B74" t="s">
+        <v>38</v>
+      </c>
+      <c r="C74" t="s">
+        <v>39</v>
+      </c>
+      <c r="D74">
+        <v>216.6</v>
+      </c>
+      <c r="E74">
+        <v>241.8</v>
+      </c>
+      <c r="F74">
+        <v>11.6</v>
+      </c>
+      <c r="G74">
+        <v>161.6</v>
+      </c>
+      <c r="H74">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8">
+      <c r="A75" t="s">
+        <v>56</v>
+      </c>
+      <c r="B75" t="s">
+        <v>30</v>
+      </c>
+      <c r="C75" t="s">
+        <v>31</v>
+      </c>
+      <c r="D75">
+        <v>148.4</v>
+      </c>
+      <c r="E75">
+        <v>164.9</v>
+      </c>
+      <c r="F75">
+        <v>11.1</v>
+      </c>
+      <c r="G75">
+        <v>161.6</v>
+      </c>
+      <c r="H75">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8">
+      <c r="A76" t="s">
+        <v>56</v>
+      </c>
+      <c r="B76" t="s">
+        <v>18</v>
+      </c>
+      <c r="C76" t="s">
+        <v>19</v>
+      </c>
+      <c r="D76">
+        <v>136.5</v>
+      </c>
+      <c r="E76">
+        <v>150.8</v>
+      </c>
+      <c r="F76">
+        <v>10.4</v>
+      </c>
+      <c r="G76" t="s">
+        <v>11</v>
+      </c>
+      <c r="H76" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8">
+      <c r="A77" t="s">
+        <v>56</v>
+      </c>
+      <c r="B77" t="s">
+        <v>43</v>
+      </c>
+      <c r="C77" t="s">
+        <v>44</v>
+      </c>
+      <c r="D77">
+        <v>168.9</v>
+      </c>
+      <c r="E77">
+        <v>185.3</v>
+      </c>
+      <c r="F77">
+        <v>9.7</v>
+      </c>
+      <c r="G77">
+        <v>161.6</v>
+      </c>
+      <c r="H77">
+        <v>14.6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8">
+      <c r="A78" t="s">
+        <v>56</v>
+      </c>
+      <c r="B78" t="s">
+        <v>28</v>
+      </c>
+      <c r="C78" t="s">
+        <v>29</v>
+      </c>
+      <c r="D78">
+        <v>227.5</v>
+      </c>
+      <c r="E78">
+        <v>249.7</v>
+      </c>
+      <c r="F78">
+        <v>9.7</v>
+      </c>
+      <c r="G78">
+        <v>161.6</v>
+      </c>
+      <c r="H78">
+        <v>54.5</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8">
+      <c r="A79" t="s">
+        <v>56</v>
+      </c>
+      <c r="B79" t="s">
+        <v>20</v>
+      </c>
+      <c r="C79" t="s">
+        <v>21</v>
+      </c>
+      <c r="D79">
+        <v>184.1</v>
+      </c>
+      <c r="E79">
+        <v>195.1</v>
+      </c>
+      <c r="F79">
+        <v>5.9</v>
+      </c>
+      <c r="G79">
+        <v>161.6</v>
+      </c>
+      <c r="H79">
+        <v>20.7</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8">
+      <c r="A80" t="s">
+        <v>56</v>
+      </c>
+      <c r="B80" t="s">
+        <v>43</v>
+      </c>
+      <c r="C80" t="s">
+        <v>45</v>
+      </c>
+      <c r="D80">
+        <v>178.2</v>
+      </c>
+      <c r="E80">
+        <v>187.2</v>
+      </c>
+      <c r="F80">
+        <v>5</v>
+      </c>
+      <c r="G80">
+        <v>161.6</v>
+      </c>
+      <c r="H80">
+        <v>15.8</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8">
+      <c r="A81" t="s">
+        <v>56</v>
+      </c>
+      <c r="B81" t="s">
+        <v>14</v>
+      </c>
+      <c r="C81" t="s">
+        <v>54</v>
+      </c>
+      <c r="D81">
+        <v>173.6</v>
+      </c>
+      <c r="E81">
+        <v>182.4</v>
+      </c>
+      <c r="F81">
+        <v>5</v>
+      </c>
+      <c r="G81">
+        <v>161.6</v>
+      </c>
+      <c r="H81">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8">
+      <c r="A82" t="s">
+        <v>56</v>
+      </c>
+      <c r="B82" t="s">
+        <v>30</v>
+      </c>
+      <c r="C82" t="s">
+        <v>50</v>
+      </c>
+      <c r="D82">
+        <v>220.3</v>
+      </c>
+      <c r="E82">
+        <v>228.1</v>
+      </c>
+      <c r="F82">
+        <v>3.5</v>
+      </c>
+      <c r="G82">
+        <v>161.6</v>
+      </c>
+      <c r="H82">
+        <v>41.1</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8">
+      <c r="A83" t="s">
+        <v>56</v>
+      </c>
+      <c r="B83" t="s">
+        <v>46</v>
+      </c>
+      <c r="C83" t="s">
+        <v>48</v>
+      </c>
+      <c r="D83">
+        <v>209.5</v>
+      </c>
+      <c r="E83">
+        <v>213.9</v>
+      </c>
+      <c r="F83">
+        <v>2</v>
+      </c>
+      <c r="G83">
+        <v>161.6</v>
+      </c>
+      <c r="H83">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8">
+      <c r="A84" t="s">
+        <v>56</v>
+      </c>
+      <c r="B84" t="s">
+        <v>14</v>
+      </c>
+      <c r="C84" t="s">
+        <v>49</v>
+      </c>
+      <c r="D84">
+        <v>180</v>
+      </c>
+      <c r="E84">
+        <v>183.7</v>
+      </c>
+      <c r="F84">
+        <v>2</v>
+      </c>
+      <c r="G84">
+        <v>161.6</v>
+      </c>
+      <c r="H84">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8">
+      <c r="A85" t="s">
+        <v>56</v>
+      </c>
+      <c r="B85" t="s">
+        <v>24</v>
+      </c>
+      <c r="C85" t="s">
+        <v>51</v>
+      </c>
+      <c r="D85">
+        <v>220.1</v>
+      </c>
+      <c r="E85">
+        <v>214.5</v>
+      </c>
+      <c r="F85">
+        <v>-2.5</v>
+      </c>
+      <c r="G85">
+        <v>161.6</v>
+      </c>
+      <c r="H85">
+        <v>32.7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8">
+      <c r="A86" t="s">
+        <v>57</v>
+      </c>
+      <c r="B86" t="s">
+        <v>14</v>
+      </c>
+      <c r="C86" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86">
+        <v>151.8</v>
+      </c>
+      <c r="E86">
+        <v>203</v>
+      </c>
+      <c r="F86">
+        <v>33.7</v>
+      </c>
+      <c r="G86">
+        <v>161.6</v>
+      </c>
+      <c r="H86">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8">
+      <c r="A87" t="s">
+        <v>57</v>
+      </c>
+      <c r="B87" t="s">
+        <v>12</v>
+      </c>
+      <c r="C87" t="s">
+        <v>13</v>
+      </c>
+      <c r="D87">
+        <v>111.5</v>
+      </c>
+      <c r="E87">
+        <v>144.3</v>
+      </c>
+      <c r="F87">
+        <v>29.4</v>
+      </c>
+      <c r="G87" t="s">
+        <v>11</v>
+      </c>
+      <c r="H87" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8">
+      <c r="A88" t="s">
+        <v>57</v>
+      </c>
+      <c r="B88" t="s">
+        <v>24</v>
+      </c>
+      <c r="C88" t="s">
+        <v>25</v>
+      </c>
+      <c r="D88">
+        <v>141.3</v>
+      </c>
+      <c r="E88">
+        <v>164.9</v>
+      </c>
+      <c r="F88">
+        <v>16.6</v>
+      </c>
+      <c r="G88">
+        <v>161.6</v>
+      </c>
+      <c r="H88">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8">
+      <c r="A89" t="s">
+        <v>57</v>
+      </c>
+      <c r="B89" t="s">
+        <v>46</v>
+      </c>
+      <c r="C89" t="s">
+        <v>53</v>
+      </c>
+      <c r="D89">
+        <v>142</v>
+      </c>
+      <c r="E89">
+        <v>164.4</v>
+      </c>
+      <c r="F89">
+        <v>15.8</v>
+      </c>
+      <c r="G89">
+        <v>161.6</v>
+      </c>
+      <c r="H89">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8">
+      <c r="A90" t="s">
+        <v>57</v>
+      </c>
+      <c r="B90" t="s">
+        <v>46</v>
+      </c>
+      <c r="C90" t="s">
+        <v>47</v>
+      </c>
+      <c r="D90">
+        <v>197.3</v>
+      </c>
+      <c r="E90">
+        <v>228.1</v>
+      </c>
+      <c r="F90">
+        <v>15.6</v>
+      </c>
+      <c r="G90">
+        <v>161.6</v>
+      </c>
+      <c r="H90">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8">
+      <c r="A91" t="s">
+        <v>57</v>
+      </c>
+      <c r="B91" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" t="s">
+        <v>10</v>
+      </c>
+      <c r="D91">
+        <v>91.2</v>
+      </c>
+      <c r="E91">
+        <v>104.4</v>
+      </c>
+      <c r="F91">
+        <v>14.4</v>
+      </c>
+      <c r="G91" t="s">
+        <v>11</v>
+      </c>
+      <c r="H91" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8">
+      <c r="A92" t="s">
+        <v>57</v>
+      </c>
+      <c r="B92" t="s">
+        <v>16</v>
+      </c>
+      <c r="C92" t="s">
+        <v>17</v>
+      </c>
+      <c r="D92">
+        <v>150.5</v>
+      </c>
+      <c r="E92">
+        <v>168.4</v>
+      </c>
+      <c r="F92">
+        <v>11.8</v>
+      </c>
+      <c r="G92">
+        <v>161.6</v>
+      </c>
+      <c r="H92">
+        <v>4.1</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8">
+      <c r="A93" t="s">
+        <v>57</v>
+      </c>
+      <c r="B93" t="s">
+        <v>26</v>
+      </c>
+      <c r="C93" t="s">
+        <v>58</v>
+      </c>
+      <c r="D93">
+        <v>94.3</v>
+      </c>
+      <c r="E93">
+        <v>105.4</v>
+      </c>
+      <c r="F93">
+        <v>11.7</v>
+      </c>
+      <c r="G93" t="s">
+        <v>11</v>
+      </c>
+      <c r="H93" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8">
+      <c r="A94" t="s">
+        <v>57</v>
+      </c>
+      <c r="B94" t="s">
+        <v>38</v>
+      </c>
+      <c r="C94" t="s">
+        <v>39</v>
+      </c>
+      <c r="D94">
+        <v>216.6</v>
+      </c>
+      <c r="E94">
+        <v>241.8</v>
+      </c>
+      <c r="F94">
+        <v>11.6</v>
+      </c>
+      <c r="G94">
+        <v>161.6</v>
+      </c>
+      <c r="H94">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8">
+      <c r="A95" t="s">
+        <v>57</v>
+      </c>
+      <c r="B95" t="s">
+        <v>28</v>
+      </c>
+      <c r="C95" t="s">
+        <v>29</v>
+      </c>
+      <c r="D95">
+        <v>227.5</v>
+      </c>
+      <c r="E95">
+        <v>252</v>
+      </c>
+      <c r="F95">
+        <v>10.7</v>
+      </c>
+      <c r="G95">
+        <v>161.6</v>
+      </c>
+      <c r="H95">
+        <v>55.8</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8">
+      <c r="A96" t="s">
+        <v>57</v>
+      </c>
+      <c r="B96" t="s">
+        <v>30</v>
+      </c>
+      <c r="C96" t="s">
+        <v>31</v>
+      </c>
+      <c r="D96">
+        <v>148.4</v>
+      </c>
+      <c r="E96">
+        <v>164.1</v>
+      </c>
+      <c r="F96">
+        <v>10.6</v>
+      </c>
+      <c r="G96">
+        <v>161.6</v>
+      </c>
+      <c r="H96">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8">
+      <c r="A97" t="s">
+        <v>57</v>
+      </c>
+      <c r="B97" t="s">
+        <v>36</v>
+      </c>
+      <c r="C97" t="s">
+        <v>37</v>
+      </c>
+      <c r="D97">
+        <v>118.4</v>
+      </c>
+      <c r="E97">
+        <v>130.9</v>
+      </c>
+      <c r="F97">
+        <v>10.5</v>
+      </c>
+      <c r="G97" t="s">
+        <v>11</v>
+      </c>
+      <c r="H97" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8">
+      <c r="A98" t="s">
+        <v>57</v>
+      </c>
+      <c r="B98" t="s">
+        <v>59</v>
+      </c>
+      <c r="C98" t="s">
+        <v>60</v>
+      </c>
+      <c r="D98">
+        <v>112.8</v>
+      </c>
+      <c r="E98">
+        <v>124.6</v>
+      </c>
+      <c r="F98">
+        <v>10.4</v>
+      </c>
+      <c r="G98" t="s">
+        <v>11</v>
+      </c>
+      <c r="H98" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8">
+      <c r="A99" t="s">
+        <v>57</v>
+      </c>
+      <c r="B99" t="s">
+        <v>43</v>
+      </c>
+      <c r="C99" t="s">
+        <v>44</v>
+      </c>
+      <c r="D99">
+        <v>168.9</v>
+      </c>
+      <c r="E99">
+        <v>186.4</v>
+      </c>
+      <c r="F99">
+        <v>10.3</v>
+      </c>
+      <c r="G99">
+        <v>161.6</v>
+      </c>
+      <c r="H99">
+        <v>15.3</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8">
+      <c r="A100" t="s">
+        <v>57</v>
+      </c>
+      <c r="B100" t="s">
+        <v>43</v>
+      </c>
+      <c r="C100" t="s">
+        <v>45</v>
+      </c>
+      <c r="D100">
+        <v>178.2</v>
+      </c>
+      <c r="E100">
+        <v>188.6</v>
+      </c>
+      <c r="F100">
+        <v>5.8</v>
+      </c>
+      <c r="G100">
+        <v>161.6</v>
+      </c>
+      <c r="H100">
+        <v>16.7</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8">
+      <c r="A101" t="s">
+        <v>57</v>
+      </c>
+      <c r="B101" t="s">
+        <v>14</v>
+      </c>
+      <c r="C101" t="s">
+        <v>54</v>
+      </c>
+      <c r="D101">
+        <v>173.6</v>
+      </c>
+      <c r="E101">
+        <v>183.5</v>
+      </c>
+      <c r="F101">
+        <v>5.7</v>
+      </c>
+      <c r="G101">
+        <v>161.6</v>
+      </c>
+      <c r="H101">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8">
+      <c r="A102" t="s">
+        <v>57</v>
+      </c>
+      <c r="B102" t="s">
+        <v>30</v>
+      </c>
+      <c r="C102" t="s">
+        <v>50</v>
+      </c>
+      <c r="D102">
+        <v>220.3</v>
+      </c>
+      <c r="E102">
+        <v>230.9</v>
+      </c>
+      <c r="F102">
+        <v>4.8</v>
+      </c>
+      <c r="G102">
+        <v>161.6</v>
+      </c>
+      <c r="H102">
+        <v>42.8</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8">
+      <c r="A103" t="s">
+        <v>57</v>
+      </c>
+      <c r="B103" t="s">
+        <v>46</v>
+      </c>
+      <c r="C103" t="s">
+        <v>48</v>
+      </c>
+      <c r="D103">
+        <v>209.5</v>
+      </c>
+      <c r="E103">
+        <v>214.2</v>
+      </c>
+      <c r="F103">
+        <v>2.2</v>
+      </c>
+      <c r="G103">
+        <v>161.6</v>
+      </c>
+      <c r="H103">
+        <v>32.5</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8">
+      <c r="A104" t="s">
+        <v>57</v>
+      </c>
+      <c r="B104" t="s">
+        <v>14</v>
+      </c>
+      <c r="C104" t="s">
+        <v>49</v>
+      </c>
+      <c r="D104">
+        <v>180</v>
+      </c>
+      <c r="E104">
+        <v>183.6</v>
+      </c>
+      <c r="F104">
+        <v>2</v>
+      </c>
+      <c r="G104">
+        <v>161.6</v>
+      </c>
+      <c r="H104">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8">
+      <c r="A105" t="s">
+        <v>57</v>
+      </c>
+      <c r="B105" t="s">
+        <v>20</v>
+      </c>
+      <c r="C105" t="s">
+        <v>21</v>
+      </c>
+      <c r="D105">
+        <v>184.1</v>
+      </c>
+      <c r="E105">
+        <v>183.5</v>
+      </c>
+      <c r="F105">
+        <v>-0.3</v>
+      </c>
+      <c r="G105">
+        <v>161.6</v>
+      </c>
+      <c r="H105">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8">
+      <c r="A106" t="s">
+        <v>57</v>
+      </c>
+      <c r="B106" t="s">
+        <v>24</v>
+      </c>
+      <c r="C106" t="s">
+        <v>51</v>
+      </c>
+      <c r="D106">
+        <v>220.1</v>
+      </c>
+      <c r="E106">
+        <v>211.6</v>
+      </c>
+      <c r="F106">
+        <v>-3.8</v>
+      </c>
+      <c r="G106">
+        <v>161.6</v>
+      </c>
+      <c r="H106">
+        <v>30.9</v>
+      </c>
+    </row>
   </sheetData>
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H65" etc:filterBottomFollowUsedRange="0">
+    <extLst/>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>

--- a/source/8、绩效异常岗位/2、卸车岗/卸车岗-6月.xlsx
+++ b/source/8、绩效异常岗位/2、卸车岗/卸车岗-6月.xlsx
@@ -12,7 +12,7 @@
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$127</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$H$168</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -32,7 +32,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="759" uniqueCount="70">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1227" uniqueCount="76">
   <si>
     <t>岗位类型</t>
   </si>
@@ -242,6 +242,24 @@
   </si>
   <si>
     <t>济南</t>
+  </si>
+  <si>
+    <t>2026-06-09</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
+  </si>
+  <si>
+    <t>2026-06-11</t>
+  </si>
+  <si>
+    <t>2026-06-12</t>
+  </si>
+  <si>
+    <t>2026-06-13</t>
+  </si>
+  <si>
+    <t>2026-06-14</t>
   </si>
 </sst>
 </file>
@@ -1172,7 +1190,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I168"/>
+  <dimension ref="A1:I273"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <sheetData>
     <row r="1" spans="1:9">
@@ -6047,8 +6065,3053 @@
         <v>29.7</v>
       </c>
     </row>
+    <row r="169" spans="1:9">
+      <c r="A169" t="s">
+        <v>9</v>
+      </c>
+      <c r="B169" t="s">
+        <v>70</v>
+      </c>
+      <c r="C169" t="s">
+        <v>16</v>
+      </c>
+      <c r="D169" t="s">
+        <v>17</v>
+      </c>
+      <c r="E169">
+        <v>151.8</v>
+      </c>
+      <c r="F169">
+        <v>199.6</v>
+      </c>
+      <c r="G169">
+        <v>31.5</v>
+      </c>
+      <c r="H169">
+        <v>159.2</v>
+      </c>
+      <c r="I169">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:9">
+      <c r="A170" t="s">
+        <v>9</v>
+      </c>
+      <c r="B170" t="s">
+        <v>70</v>
+      </c>
+      <c r="C170" t="s">
+        <v>48</v>
+      </c>
+      <c r="D170" t="s">
+        <v>55</v>
+      </c>
+      <c r="E170">
+        <v>142</v>
+      </c>
+      <c r="F170">
+        <v>160.9</v>
+      </c>
+      <c r="G170">
+        <v>13.3</v>
+      </c>
+      <c r="H170">
+        <v>159.2</v>
+      </c>
+      <c r="I170">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:9">
+      <c r="A171" t="s">
+        <v>9</v>
+      </c>
+      <c r="B171" t="s">
+        <v>70</v>
+      </c>
+      <c r="C171" t="s">
+        <v>28</v>
+      </c>
+      <c r="D171" t="s">
+        <v>60</v>
+      </c>
+      <c r="E171">
+        <v>93.7</v>
+      </c>
+      <c r="F171">
+        <v>104.9</v>
+      </c>
+      <c r="G171">
+        <v>11.9</v>
+      </c>
+      <c r="H171" t="s">
+        <v>13</v>
+      </c>
+      <c r="I171" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="172" spans="1:9">
+      <c r="A172" t="s">
+        <v>9</v>
+      </c>
+      <c r="B172" t="s">
+        <v>70</v>
+      </c>
+      <c r="C172" t="s">
+        <v>48</v>
+      </c>
+      <c r="D172" t="s">
+        <v>49</v>
+      </c>
+      <c r="E172">
+        <v>197.3</v>
+      </c>
+      <c r="F172">
+        <v>220.7</v>
+      </c>
+      <c r="G172">
+        <v>11.8</v>
+      </c>
+      <c r="H172">
+        <v>159.2</v>
+      </c>
+      <c r="I172">
+        <v>38.6</v>
+      </c>
+    </row>
+    <row r="173" spans="1:9">
+      <c r="A173" t="s">
+        <v>9</v>
+      </c>
+      <c r="B173" t="s">
+        <v>70</v>
+      </c>
+      <c r="C173" t="s">
+        <v>11</v>
+      </c>
+      <c r="D173" t="s">
+        <v>12</v>
+      </c>
+      <c r="E173">
+        <v>91.2</v>
+      </c>
+      <c r="F173">
+        <v>101.5</v>
+      </c>
+      <c r="G173">
+        <v>11.3</v>
+      </c>
+      <c r="H173" t="s">
+        <v>13</v>
+      </c>
+      <c r="I173" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="174" spans="1:9">
+      <c r="A174" t="s">
+        <v>9</v>
+      </c>
+      <c r="B174" t="s">
+        <v>70</v>
+      </c>
+      <c r="C174" t="s">
+        <v>30</v>
+      </c>
+      <c r="D174" t="s">
+        <v>31</v>
+      </c>
+      <c r="E174">
+        <v>227.5</v>
+      </c>
+      <c r="F174">
+        <v>252.6</v>
+      </c>
+      <c r="G174">
+        <v>11</v>
+      </c>
+      <c r="H174">
+        <v>159.2</v>
+      </c>
+      <c r="I174">
+        <v>58.6</v>
+      </c>
+    </row>
+    <row r="175" spans="1:9">
+      <c r="A175" t="s">
+        <v>9</v>
+      </c>
+      <c r="B175" t="s">
+        <v>70</v>
+      </c>
+      <c r="C175" t="s">
+        <v>14</v>
+      </c>
+      <c r="D175" t="s">
+        <v>15</v>
+      </c>
+      <c r="E175">
+        <v>117</v>
+      </c>
+      <c r="F175">
+        <v>129.4</v>
+      </c>
+      <c r="G175">
+        <v>10.5</v>
+      </c>
+      <c r="H175" t="s">
+        <v>13</v>
+      </c>
+      <c r="I175" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="176" spans="1:9">
+      <c r="A176" t="s">
+        <v>9</v>
+      </c>
+      <c r="B176" t="s">
+        <v>70</v>
+      </c>
+      <c r="C176" t="s">
+        <v>32</v>
+      </c>
+      <c r="D176" t="s">
+        <v>69</v>
+      </c>
+      <c r="E176">
+        <v>134.3</v>
+      </c>
+      <c r="F176">
+        <v>148</v>
+      </c>
+      <c r="G176">
+        <v>10.2</v>
+      </c>
+      <c r="H176" t="s">
+        <v>13</v>
+      </c>
+      <c r="I176" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="177" spans="1:9">
+      <c r="A177" t="s">
+        <v>9</v>
+      </c>
+      <c r="B177" t="s">
+        <v>70</v>
+      </c>
+      <c r="C177" t="s">
+        <v>64</v>
+      </c>
+      <c r="D177" t="s">
+        <v>65</v>
+      </c>
+      <c r="E177">
+        <v>120.5</v>
+      </c>
+      <c r="F177">
+        <v>132.8</v>
+      </c>
+      <c r="G177">
+        <v>10.2</v>
+      </c>
+      <c r="H177" t="s">
+        <v>13</v>
+      </c>
+      <c r="I177" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="178" spans="1:9">
+      <c r="A178" t="s">
+        <v>9</v>
+      </c>
+      <c r="B178" t="s">
+        <v>70</v>
+      </c>
+      <c r="C178" t="s">
+        <v>26</v>
+      </c>
+      <c r="D178" t="s">
+        <v>27</v>
+      </c>
+      <c r="E178">
+        <v>141.3</v>
+      </c>
+      <c r="F178">
+        <v>155.7</v>
+      </c>
+      <c r="G178">
+        <v>10.1</v>
+      </c>
+      <c r="H178" t="s">
+        <v>13</v>
+      </c>
+      <c r="I178" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="179" spans="1:9">
+      <c r="A179" t="s">
+        <v>9</v>
+      </c>
+      <c r="B179" t="s">
+        <v>70</v>
+      </c>
+      <c r="C179" t="s">
+        <v>32</v>
+      </c>
+      <c r="D179" t="s">
+        <v>33</v>
+      </c>
+      <c r="E179">
+        <v>148.4</v>
+      </c>
+      <c r="F179">
+        <v>163.3</v>
+      </c>
+      <c r="G179">
+        <v>10</v>
+      </c>
+      <c r="H179">
+        <v>159.2</v>
+      </c>
+      <c r="I179">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="180" spans="1:9">
+      <c r="A180" t="s">
+        <v>9</v>
+      </c>
+      <c r="B180" t="s">
+        <v>70</v>
+      </c>
+      <c r="C180" t="s">
+        <v>40</v>
+      </c>
+      <c r="D180" t="s">
+        <v>41</v>
+      </c>
+      <c r="E180">
+        <v>216.6</v>
+      </c>
+      <c r="F180">
+        <v>238.2</v>
+      </c>
+      <c r="G180">
+        <v>10</v>
+      </c>
+      <c r="H180">
+        <v>159.2</v>
+      </c>
+      <c r="I180">
+        <v>49.6</v>
+      </c>
+    </row>
+    <row r="181" spans="1:9">
+      <c r="A181" t="s">
+        <v>9</v>
+      </c>
+      <c r="B181" t="s">
+        <v>70</v>
+      </c>
+      <c r="C181" t="s">
+        <v>32</v>
+      </c>
+      <c r="D181" t="s">
+        <v>52</v>
+      </c>
+      <c r="E181">
+        <v>220.3</v>
+      </c>
+      <c r="F181">
+        <v>235.3</v>
+      </c>
+      <c r="G181">
+        <v>6.8</v>
+      </c>
+      <c r="H181">
+        <v>159.2</v>
+      </c>
+      <c r="I181">
+        <v>47.8</v>
+      </c>
+    </row>
+    <row r="182" spans="1:9">
+      <c r="A182" t="s">
+        <v>9</v>
+      </c>
+      <c r="B182" t="s">
+        <v>70</v>
+      </c>
+      <c r="C182" t="s">
+        <v>32</v>
+      </c>
+      <c r="D182" t="s">
+        <v>67</v>
+      </c>
+      <c r="E182">
+        <v>168.1</v>
+      </c>
+      <c r="F182">
+        <v>178.8</v>
+      </c>
+      <c r="G182">
+        <v>6.3</v>
+      </c>
+      <c r="H182">
+        <v>159.2</v>
+      </c>
+      <c r="I182">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="183" spans="1:9">
+      <c r="A183" t="s">
+        <v>9</v>
+      </c>
+      <c r="B183" t="s">
+        <v>70</v>
+      </c>
+      <c r="C183" t="s">
+        <v>16</v>
+      </c>
+      <c r="D183" t="s">
+        <v>56</v>
+      </c>
+      <c r="E183">
+        <v>173.6</v>
+      </c>
+      <c r="F183">
+        <v>180.2</v>
+      </c>
+      <c r="G183">
+        <v>3.8</v>
+      </c>
+      <c r="H183">
+        <v>159.2</v>
+      </c>
+      <c r="I183">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="184" spans="1:9">
+      <c r="A184" t="s">
+        <v>9</v>
+      </c>
+      <c r="B184" t="s">
+        <v>70</v>
+      </c>
+      <c r="C184" t="s">
+        <v>45</v>
+      </c>
+      <c r="D184" t="s">
+        <v>47</v>
+      </c>
+      <c r="E184">
+        <v>178.2</v>
+      </c>
+      <c r="F184">
+        <v>182.6</v>
+      </c>
+      <c r="G184">
+        <v>2.4</v>
+      </c>
+      <c r="H184">
+        <v>159.2</v>
+      </c>
+      <c r="I184">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="185" spans="1:9">
+      <c r="A185" t="s">
+        <v>9</v>
+      </c>
+      <c r="B185" t="s">
+        <v>70</v>
+      </c>
+      <c r="C185" t="s">
+        <v>45</v>
+      </c>
+      <c r="D185" t="s">
+        <v>46</v>
+      </c>
+      <c r="E185">
+        <v>176.6</v>
+      </c>
+      <c r="F185">
+        <v>180.9</v>
+      </c>
+      <c r="G185">
+        <v>2.4</v>
+      </c>
+      <c r="H185">
+        <v>159.2</v>
+      </c>
+      <c r="I185">
+        <v>13.6</v>
+      </c>
+    </row>
+    <row r="186" spans="1:9">
+      <c r="A186" t="s">
+        <v>9</v>
+      </c>
+      <c r="B186" t="s">
+        <v>70</v>
+      </c>
+      <c r="C186" t="s">
+        <v>48</v>
+      </c>
+      <c r="D186" t="s">
+        <v>50</v>
+      </c>
+      <c r="E186">
+        <v>209.5</v>
+      </c>
+      <c r="F186">
+        <v>210</v>
+      </c>
+      <c r="G186">
+        <v>0.2</v>
+      </c>
+      <c r="H186">
+        <v>159.2</v>
+      </c>
+      <c r="I186">
+        <v>31.9</v>
+      </c>
+    </row>
+    <row r="187" spans="1:9">
+      <c r="A187" t="s">
+        <v>9</v>
+      </c>
+      <c r="B187" t="s">
+        <v>70</v>
+      </c>
+      <c r="C187" t="s">
+        <v>16</v>
+      </c>
+      <c r="D187" t="s">
+        <v>51</v>
+      </c>
+      <c r="E187">
+        <v>180</v>
+      </c>
+      <c r="F187">
+        <v>179.5</v>
+      </c>
+      <c r="G187">
+        <v>-0.2</v>
+      </c>
+      <c r="H187">
+        <v>159.2</v>
+      </c>
+      <c r="I187">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="188" spans="1:9">
+      <c r="A188" t="s">
+        <v>9</v>
+      </c>
+      <c r="B188" t="s">
+        <v>70</v>
+      </c>
+      <c r="C188" t="s">
+        <v>22</v>
+      </c>
+      <c r="D188" t="s">
+        <v>23</v>
+      </c>
+      <c r="E188">
+        <v>184.1</v>
+      </c>
+      <c r="F188">
+        <v>175.6</v>
+      </c>
+      <c r="G188">
+        <v>-4.6</v>
+      </c>
+      <c r="H188">
+        <v>159.2</v>
+      </c>
+      <c r="I188">
+        <v>10.3</v>
+      </c>
+    </row>
+    <row r="189" spans="1:9">
+      <c r="A189" t="s">
+        <v>9</v>
+      </c>
+      <c r="B189" t="s">
+        <v>70</v>
+      </c>
+      <c r="C189" t="s">
+        <v>26</v>
+      </c>
+      <c r="D189" t="s">
+        <v>53</v>
+      </c>
+      <c r="E189">
+        <v>220.1</v>
+      </c>
+      <c r="F189">
+        <v>207.1</v>
+      </c>
+      <c r="G189">
+        <v>-5.9</v>
+      </c>
+      <c r="H189">
+        <v>159.2</v>
+      </c>
+      <c r="I189">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="190" spans="1:9">
+      <c r="A190" t="s">
+        <v>9</v>
+      </c>
+      <c r="B190" t="s">
+        <v>71</v>
+      </c>
+      <c r="C190" t="s">
+        <v>16</v>
+      </c>
+      <c r="D190" t="s">
+        <v>17</v>
+      </c>
+      <c r="E190">
+        <v>151.8</v>
+      </c>
+      <c r="F190">
+        <v>200.2</v>
+      </c>
+      <c r="G190">
+        <v>31.8</v>
+      </c>
+      <c r="H190">
+        <v>159.4</v>
+      </c>
+      <c r="I190">
+        <v>25.6</v>
+      </c>
+    </row>
+    <row r="191" spans="1:9">
+      <c r="A191" t="s">
+        <v>9</v>
+      </c>
+      <c r="B191" t="s">
+        <v>71</v>
+      </c>
+      <c r="C191" t="s">
+        <v>48</v>
+      </c>
+      <c r="D191" t="s">
+        <v>55</v>
+      </c>
+      <c r="E191">
+        <v>142</v>
+      </c>
+      <c r="F191">
+        <v>161.2</v>
+      </c>
+      <c r="G191">
+        <v>13.5</v>
+      </c>
+      <c r="H191">
+        <v>159.4</v>
+      </c>
+      <c r="I191">
+        <v>1.1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:9">
+      <c r="A192" t="s">
+        <v>9</v>
+      </c>
+      <c r="B192" t="s">
+        <v>71</v>
+      </c>
+      <c r="C192" t="s">
+        <v>28</v>
+      </c>
+      <c r="D192" t="s">
+        <v>60</v>
+      </c>
+      <c r="E192">
+        <v>93.7</v>
+      </c>
+      <c r="F192">
+        <v>104.9</v>
+      </c>
+      <c r="G192">
+        <v>11.9</v>
+      </c>
+      <c r="H192" t="s">
+        <v>13</v>
+      </c>
+      <c r="I192" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="193" spans="1:9">
+      <c r="A193" t="s">
+        <v>9</v>
+      </c>
+      <c r="B193" t="s">
+        <v>71</v>
+      </c>
+      <c r="C193" t="s">
+        <v>30</v>
+      </c>
+      <c r="D193" t="s">
+        <v>31</v>
+      </c>
+      <c r="E193">
+        <v>227.5</v>
+      </c>
+      <c r="F193">
+        <v>254.3</v>
+      </c>
+      <c r="G193">
+        <v>11.7</v>
+      </c>
+      <c r="H193">
+        <v>159.4</v>
+      </c>
+      <c r="I193">
+        <v>59.5</v>
+      </c>
+    </row>
+    <row r="194" spans="1:9">
+      <c r="A194" t="s">
+        <v>9</v>
+      </c>
+      <c r="B194" t="s">
+        <v>71</v>
+      </c>
+      <c r="C194" t="s">
+        <v>48</v>
+      </c>
+      <c r="D194" t="s">
+        <v>49</v>
+      </c>
+      <c r="E194">
+        <v>197.3</v>
+      </c>
+      <c r="F194">
+        <v>219.9</v>
+      </c>
+      <c r="G194">
+        <v>11.4</v>
+      </c>
+      <c r="H194">
+        <v>159.4</v>
+      </c>
+      <c r="I194">
+        <v>37.9</v>
+      </c>
+    </row>
+    <row r="195" spans="1:9">
+      <c r="A195" t="s">
+        <v>9</v>
+      </c>
+      <c r="B195" t="s">
+        <v>71</v>
+      </c>
+      <c r="C195" t="s">
+        <v>32</v>
+      </c>
+      <c r="D195" t="s">
+        <v>69</v>
+      </c>
+      <c r="E195">
+        <v>134.3</v>
+      </c>
+      <c r="F195">
+        <v>149.4</v>
+      </c>
+      <c r="G195">
+        <v>11.2</v>
+      </c>
+      <c r="H195" t="s">
+        <v>13</v>
+      </c>
+      <c r="I195" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="196" spans="1:9">
+      <c r="A196" t="s">
+        <v>9</v>
+      </c>
+      <c r="B196" t="s">
+        <v>71</v>
+      </c>
+      <c r="C196" t="s">
+        <v>14</v>
+      </c>
+      <c r="D196" t="s">
+        <v>15</v>
+      </c>
+      <c r="E196">
+        <v>117</v>
+      </c>
+      <c r="F196">
+        <v>130.1</v>
+      </c>
+      <c r="G196">
+        <v>11.1</v>
+      </c>
+      <c r="H196" t="s">
+        <v>13</v>
+      </c>
+      <c r="I196" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="197" spans="1:9">
+      <c r="A197" t="s">
+        <v>9</v>
+      </c>
+      <c r="B197" t="s">
+        <v>71</v>
+      </c>
+      <c r="C197" t="s">
+        <v>32</v>
+      </c>
+      <c r="D197" t="s">
+        <v>33</v>
+      </c>
+      <c r="E197">
+        <v>148.4</v>
+      </c>
+      <c r="F197">
+        <v>163.7</v>
+      </c>
+      <c r="G197">
+        <v>10.3</v>
+      </c>
+      <c r="H197">
+        <v>159.4</v>
+      </c>
+      <c r="I197">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="198" spans="1:9">
+      <c r="A198" t="s">
+        <v>9</v>
+      </c>
+      <c r="B198" t="s">
+        <v>71</v>
+      </c>
+      <c r="C198" t="s">
+        <v>61</v>
+      </c>
+      <c r="D198" t="s">
+        <v>62</v>
+      </c>
+      <c r="E198">
+        <v>112.8</v>
+      </c>
+      <c r="F198">
+        <v>124.5</v>
+      </c>
+      <c r="G198">
+        <v>10.3</v>
+      </c>
+      <c r="H198" t="s">
+        <v>13</v>
+      </c>
+      <c r="I198" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9">
+      <c r="A199" t="s">
+        <v>9</v>
+      </c>
+      <c r="B199" t="s">
+        <v>71</v>
+      </c>
+      <c r="C199" t="s">
+        <v>11</v>
+      </c>
+      <c r="D199" t="s">
+        <v>12</v>
+      </c>
+      <c r="E199">
+        <v>91.2</v>
+      </c>
+      <c r="F199">
+        <v>100.5</v>
+      </c>
+      <c r="G199">
+        <v>10.2</v>
+      </c>
+      <c r="H199" t="s">
+        <v>13</v>
+      </c>
+      <c r="I199" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="200" spans="1:9">
+      <c r="A200" t="s">
+        <v>9</v>
+      </c>
+      <c r="B200" t="s">
+        <v>71</v>
+      </c>
+      <c r="C200" t="s">
+        <v>40</v>
+      </c>
+      <c r="D200" t="s">
+        <v>41</v>
+      </c>
+      <c r="E200">
+        <v>216.6</v>
+      </c>
+      <c r="F200">
+        <v>237.9</v>
+      </c>
+      <c r="G200">
+        <v>9.8</v>
+      </c>
+      <c r="H200">
+        <v>159.4</v>
+      </c>
+      <c r="I200">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="201" spans="1:9">
+      <c r="A201" t="s">
+        <v>9</v>
+      </c>
+      <c r="B201" t="s">
+        <v>71</v>
+      </c>
+      <c r="C201" t="s">
+        <v>32</v>
+      </c>
+      <c r="D201" t="s">
+        <v>52</v>
+      </c>
+      <c r="E201">
+        <v>220.3</v>
+      </c>
+      <c r="F201">
+        <v>237.2</v>
+      </c>
+      <c r="G201">
+        <v>7.6</v>
+      </c>
+      <c r="H201">
+        <v>159.4</v>
+      </c>
+      <c r="I201">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="202" spans="1:9">
+      <c r="A202" t="s">
+        <v>9</v>
+      </c>
+      <c r="B202" t="s">
+        <v>71</v>
+      </c>
+      <c r="C202" t="s">
+        <v>32</v>
+      </c>
+      <c r="D202" t="s">
+        <v>67</v>
+      </c>
+      <c r="E202">
+        <v>168.1</v>
+      </c>
+      <c r="F202">
+        <v>179</v>
+      </c>
+      <c r="G202">
+        <v>6.5</v>
+      </c>
+      <c r="H202">
+        <v>159.4</v>
+      </c>
+      <c r="I202">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="203" spans="1:9">
+      <c r="A203" t="s">
+        <v>9</v>
+      </c>
+      <c r="B203" t="s">
+        <v>71</v>
+      </c>
+      <c r="C203" t="s">
+        <v>16</v>
+      </c>
+      <c r="D203" t="s">
+        <v>56</v>
+      </c>
+      <c r="E203">
+        <v>173.6</v>
+      </c>
+      <c r="F203">
+        <v>180.4</v>
+      </c>
+      <c r="G203">
+        <v>3.9</v>
+      </c>
+      <c r="H203">
+        <v>159.4</v>
+      </c>
+      <c r="I203">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="204" spans="1:9">
+      <c r="A204" t="s">
+        <v>9</v>
+      </c>
+      <c r="B204" t="s">
+        <v>71</v>
+      </c>
+      <c r="C204" t="s">
+        <v>45</v>
+      </c>
+      <c r="D204" t="s">
+        <v>47</v>
+      </c>
+      <c r="E204">
+        <v>178.2</v>
+      </c>
+      <c r="F204">
+        <v>182.9</v>
+      </c>
+      <c r="G204">
+        <v>2.6</v>
+      </c>
+      <c r="H204">
+        <v>159.4</v>
+      </c>
+      <c r="I204">
+        <v>14.7</v>
+      </c>
+    </row>
+    <row r="205" spans="1:9">
+      <c r="A205" t="s">
+        <v>9</v>
+      </c>
+      <c r="B205" t="s">
+        <v>71</v>
+      </c>
+      <c r="C205" t="s">
+        <v>45</v>
+      </c>
+      <c r="D205" t="s">
+        <v>46</v>
+      </c>
+      <c r="E205">
+        <v>176.6</v>
+      </c>
+      <c r="F205">
+        <v>180.6</v>
+      </c>
+      <c r="G205">
+        <v>2.2</v>
+      </c>
+      <c r="H205">
+        <v>159.4</v>
+      </c>
+      <c r="I205">
+        <v>13.3</v>
+      </c>
+    </row>
+    <row r="206" spans="1:9">
+      <c r="A206" t="s">
+        <v>9</v>
+      </c>
+      <c r="B206" t="s">
+        <v>71</v>
+      </c>
+      <c r="C206" t="s">
+        <v>48</v>
+      </c>
+      <c r="D206" t="s">
+        <v>50</v>
+      </c>
+      <c r="E206">
+        <v>209.5</v>
+      </c>
+      <c r="F206">
+        <v>209.8</v>
+      </c>
+      <c r="G206">
+        <v>0.1</v>
+      </c>
+      <c r="H206">
+        <v>159.4</v>
+      </c>
+      <c r="I206">
+        <v>31.6</v>
+      </c>
+    </row>
+    <row r="207" spans="1:9">
+      <c r="A207" t="s">
+        <v>9</v>
+      </c>
+      <c r="B207" t="s">
+        <v>71</v>
+      </c>
+      <c r="C207" t="s">
+        <v>16</v>
+      </c>
+      <c r="D207" t="s">
+        <v>51</v>
+      </c>
+      <c r="E207">
+        <v>180</v>
+      </c>
+      <c r="F207">
+        <v>179.6</v>
+      </c>
+      <c r="G207">
+        <v>-0.1</v>
+      </c>
+      <c r="H207">
+        <v>159.4</v>
+      </c>
+      <c r="I207">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="208" spans="1:9">
+      <c r="A208" t="s">
+        <v>9</v>
+      </c>
+      <c r="B208" t="s">
+        <v>71</v>
+      </c>
+      <c r="C208" t="s">
+        <v>26</v>
+      </c>
+      <c r="D208" t="s">
+        <v>53</v>
+      </c>
+      <c r="E208">
+        <v>220.1</v>
+      </c>
+      <c r="F208">
+        <v>206.5</v>
+      </c>
+      <c r="G208">
+        <v>-6.1</v>
+      </c>
+      <c r="H208">
+        <v>159.4</v>
+      </c>
+      <c r="I208">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="209" spans="1:9">
+      <c r="A209" t="s">
+        <v>9</v>
+      </c>
+      <c r="B209" t="s">
+        <v>72</v>
+      </c>
+      <c r="C209" t="s">
+        <v>16</v>
+      </c>
+      <c r="D209" t="s">
+        <v>17</v>
+      </c>
+      <c r="E209">
+        <v>151.8</v>
+      </c>
+      <c r="F209">
+        <v>200.3</v>
+      </c>
+      <c r="G209">
+        <v>31.9</v>
+      </c>
+      <c r="H209">
+        <v>159.6</v>
+      </c>
+      <c r="I209">
+        <v>25.5</v>
+      </c>
+    </row>
+    <row r="210" spans="1:9">
+      <c r="A210" t="s">
+        <v>9</v>
+      </c>
+      <c r="B210" t="s">
+        <v>72</v>
+      </c>
+      <c r="C210" t="s">
+        <v>28</v>
+      </c>
+      <c r="D210" t="s">
+        <v>60</v>
+      </c>
+      <c r="E210">
+        <v>93.6</v>
+      </c>
+      <c r="F210">
+        <v>106.3</v>
+      </c>
+      <c r="G210">
+        <v>13.5</v>
+      </c>
+      <c r="H210" t="s">
+        <v>13</v>
+      </c>
+      <c r="I210" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="211" spans="1:9">
+      <c r="A211" t="s">
+        <v>9</v>
+      </c>
+      <c r="B211" t="s">
+        <v>72</v>
+      </c>
+      <c r="C211" t="s">
+        <v>48</v>
+      </c>
+      <c r="D211" t="s">
+        <v>55</v>
+      </c>
+      <c r="E211">
+        <v>142</v>
+      </c>
+      <c r="F211">
+        <v>160.8</v>
+      </c>
+      <c r="G211">
+        <v>13.2</v>
+      </c>
+      <c r="H211">
+        <v>159.6</v>
+      </c>
+      <c r="I211">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="212" spans="1:9">
+      <c r="A212" t="s">
+        <v>9</v>
+      </c>
+      <c r="B212" t="s">
+        <v>72</v>
+      </c>
+      <c r="C212" t="s">
+        <v>30</v>
+      </c>
+      <c r="D212" t="s">
+        <v>31</v>
+      </c>
+      <c r="E212">
+        <v>227.5</v>
+      </c>
+      <c r="F212">
+        <v>255.4</v>
+      </c>
+      <c r="G212">
+        <v>12.2</v>
+      </c>
+      <c r="H212">
+        <v>159.6</v>
+      </c>
+      <c r="I212">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="213" spans="1:9">
+      <c r="A213" t="s">
+        <v>9</v>
+      </c>
+      <c r="B213" t="s">
+        <v>72</v>
+      </c>
+      <c r="C213" t="s">
+        <v>48</v>
+      </c>
+      <c r="D213" t="s">
+        <v>49</v>
+      </c>
+      <c r="E213">
+        <v>197.3</v>
+      </c>
+      <c r="F213">
+        <v>219.7</v>
+      </c>
+      <c r="G213">
+        <v>11.3</v>
+      </c>
+      <c r="H213">
+        <v>159.6</v>
+      </c>
+      <c r="I213">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="214" spans="1:9">
+      <c r="A214" t="s">
+        <v>9</v>
+      </c>
+      <c r="B214" t="s">
+        <v>72</v>
+      </c>
+      <c r="C214" t="s">
+        <v>32</v>
+      </c>
+      <c r="D214" t="s">
+        <v>69</v>
+      </c>
+      <c r="E214">
+        <v>134.3</v>
+      </c>
+      <c r="F214">
+        <v>149.5</v>
+      </c>
+      <c r="G214">
+        <v>11.3</v>
+      </c>
+      <c r="H214" t="s">
+        <v>13</v>
+      </c>
+      <c r="I214" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="215" spans="1:9">
+      <c r="A215" t="s">
+        <v>9</v>
+      </c>
+      <c r="B215" t="s">
+        <v>72</v>
+      </c>
+      <c r="C215" t="s">
+        <v>32</v>
+      </c>
+      <c r="D215" t="s">
+        <v>33</v>
+      </c>
+      <c r="E215">
+        <v>148.4</v>
+      </c>
+      <c r="F215">
+        <v>163.8</v>
+      </c>
+      <c r="G215">
+        <v>10.4</v>
+      </c>
+      <c r="H215">
+        <v>159.6</v>
+      </c>
+      <c r="I215">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="216" spans="1:9">
+      <c r="A216" t="s">
+        <v>9</v>
+      </c>
+      <c r="B216" t="s">
+        <v>72</v>
+      </c>
+      <c r="C216" t="s">
+        <v>26</v>
+      </c>
+      <c r="D216" t="s">
+        <v>27</v>
+      </c>
+      <c r="E216">
+        <v>141.3</v>
+      </c>
+      <c r="F216">
+        <v>155.5</v>
+      </c>
+      <c r="G216">
+        <v>10</v>
+      </c>
+      <c r="H216" t="s">
+        <v>13</v>
+      </c>
+      <c r="I216" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="217" spans="1:9">
+      <c r="A217" t="s">
+        <v>9</v>
+      </c>
+      <c r="B217" t="s">
+        <v>72</v>
+      </c>
+      <c r="C217" t="s">
+        <v>40</v>
+      </c>
+      <c r="D217" t="s">
+        <v>41</v>
+      </c>
+      <c r="E217">
+        <v>216.6</v>
+      </c>
+      <c r="F217">
+        <v>238.1</v>
+      </c>
+      <c r="G217">
+        <v>9.9</v>
+      </c>
+      <c r="H217">
+        <v>159.6</v>
+      </c>
+      <c r="I217">
+        <v>49.1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:9">
+      <c r="A218" t="s">
+        <v>9</v>
+      </c>
+      <c r="B218" t="s">
+        <v>72</v>
+      </c>
+      <c r="C218" t="s">
+        <v>32</v>
+      </c>
+      <c r="D218" t="s">
+        <v>52</v>
+      </c>
+      <c r="E218">
+        <v>220.3</v>
+      </c>
+      <c r="F218">
+        <v>238.2</v>
+      </c>
+      <c r="G218">
+        <v>8.1</v>
+      </c>
+      <c r="H218">
+        <v>159.6</v>
+      </c>
+      <c r="I218">
+        <v>49.2</v>
+      </c>
+    </row>
+    <row r="219" spans="1:9">
+      <c r="A219" t="s">
+        <v>9</v>
+      </c>
+      <c r="B219" t="s">
+        <v>72</v>
+      </c>
+      <c r="C219" t="s">
+        <v>32</v>
+      </c>
+      <c r="D219" t="s">
+        <v>67</v>
+      </c>
+      <c r="E219">
+        <v>168.1</v>
+      </c>
+      <c r="F219">
+        <v>179.3</v>
+      </c>
+      <c r="G219">
+        <v>6.6</v>
+      </c>
+      <c r="H219">
+        <v>159.6</v>
+      </c>
+      <c r="I219">
+        <v>12.3</v>
+      </c>
+    </row>
+    <row r="220" spans="1:9">
+      <c r="A220" t="s">
+        <v>9</v>
+      </c>
+      <c r="B220" t="s">
+        <v>72</v>
+      </c>
+      <c r="C220" t="s">
+        <v>16</v>
+      </c>
+      <c r="D220" t="s">
+        <v>56</v>
+      </c>
+      <c r="E220">
+        <v>173.6</v>
+      </c>
+      <c r="F220">
+        <v>180.5</v>
+      </c>
+      <c r="G220">
+        <v>3.9</v>
+      </c>
+      <c r="H220">
+        <v>159.6</v>
+      </c>
+      <c r="I220">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="221" spans="1:9">
+      <c r="A221" t="s">
+        <v>9</v>
+      </c>
+      <c r="B221" t="s">
+        <v>72</v>
+      </c>
+      <c r="C221" t="s">
+        <v>45</v>
+      </c>
+      <c r="D221" t="s">
+        <v>47</v>
+      </c>
+      <c r="E221">
+        <v>178.2</v>
+      </c>
+      <c r="F221">
+        <v>183.5</v>
+      </c>
+      <c r="G221">
+        <v>2.9</v>
+      </c>
+      <c r="H221">
+        <v>159.6</v>
+      </c>
+      <c r="I221">
+        <v>14.9</v>
+      </c>
+    </row>
+    <row r="222" spans="1:9">
+      <c r="A222" t="s">
+        <v>9</v>
+      </c>
+      <c r="B222" t="s">
+        <v>72</v>
+      </c>
+      <c r="C222" t="s">
+        <v>45</v>
+      </c>
+      <c r="D222" t="s">
+        <v>46</v>
+      </c>
+      <c r="E222">
+        <v>176.6</v>
+      </c>
+      <c r="F222">
+        <v>180.6</v>
+      </c>
+      <c r="G222">
+        <v>2.2</v>
+      </c>
+      <c r="H222">
+        <v>159.6</v>
+      </c>
+      <c r="I222">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:9">
+      <c r="A223" t="s">
+        <v>9</v>
+      </c>
+      <c r="B223" t="s">
+        <v>72</v>
+      </c>
+      <c r="C223" t="s">
+        <v>48</v>
+      </c>
+      <c r="D223" t="s">
+        <v>50</v>
+      </c>
+      <c r="E223">
+        <v>209.5</v>
+      </c>
+      <c r="F223">
+        <v>209.6</v>
+      </c>
+      <c r="G223">
+        <v>0</v>
+      </c>
+      <c r="H223">
+        <v>159.6</v>
+      </c>
+      <c r="I223">
+        <v>31.3</v>
+      </c>
+    </row>
+    <row r="224" spans="1:9">
+      <c r="A224" t="s">
+        <v>9</v>
+      </c>
+      <c r="B224" t="s">
+        <v>72</v>
+      </c>
+      <c r="C224" t="s">
+        <v>16</v>
+      </c>
+      <c r="D224" t="s">
+        <v>51</v>
+      </c>
+      <c r="E224">
+        <v>180</v>
+      </c>
+      <c r="F224">
+        <v>179.1</v>
+      </c>
+      <c r="G224">
+        <v>-0.4</v>
+      </c>
+      <c r="H224">
+        <v>159.6</v>
+      </c>
+      <c r="I224">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="225" spans="1:9">
+      <c r="A225" t="s">
+        <v>9</v>
+      </c>
+      <c r="B225" t="s">
+        <v>72</v>
+      </c>
+      <c r="C225" t="s">
+        <v>26</v>
+      </c>
+      <c r="D225" t="s">
+        <v>53</v>
+      </c>
+      <c r="E225">
+        <v>220.1</v>
+      </c>
+      <c r="F225">
+        <v>206.7</v>
+      </c>
+      <c r="G225">
+        <v>-6</v>
+      </c>
+      <c r="H225">
+        <v>159.6</v>
+      </c>
+      <c r="I225">
+        <v>29.5</v>
+      </c>
+    </row>
+    <row r="226" spans="1:9">
+      <c r="A226" t="s">
+        <v>9</v>
+      </c>
+      <c r="B226" t="s">
+        <v>73</v>
+      </c>
+      <c r="C226" t="s">
+        <v>16</v>
+      </c>
+      <c r="D226" t="s">
+        <v>17</v>
+      </c>
+      <c r="E226">
+        <v>151.8</v>
+      </c>
+      <c r="F226">
+        <v>200.1</v>
+      </c>
+      <c r="G226">
+        <v>31.8</v>
+      </c>
+      <c r="H226">
+        <v>159.5</v>
+      </c>
+      <c r="I226">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="227" spans="1:9">
+      <c r="A227" t="s">
+        <v>9</v>
+      </c>
+      <c r="B227" t="s">
+        <v>73</v>
+      </c>
+      <c r="C227" t="s">
+        <v>48</v>
+      </c>
+      <c r="D227" t="s">
+        <v>49</v>
+      </c>
+      <c r="E227">
+        <v>184.6</v>
+      </c>
+      <c r="F227">
+        <v>219</v>
+      </c>
+      <c r="G227">
+        <v>18.6</v>
+      </c>
+      <c r="H227">
+        <v>159.5</v>
+      </c>
+      <c r="I227">
+        <v>37.3</v>
+      </c>
+    </row>
+    <row r="228" spans="1:9">
+      <c r="A228" t="s">
+        <v>9</v>
+      </c>
+      <c r="B228" t="s">
+        <v>73</v>
+      </c>
+      <c r="C228" t="s">
+        <v>28</v>
+      </c>
+      <c r="D228" t="s">
+        <v>60</v>
+      </c>
+      <c r="E228">
+        <v>93.6</v>
+      </c>
+      <c r="F228">
+        <v>106.4</v>
+      </c>
+      <c r="G228">
+        <v>13.6</v>
+      </c>
+      <c r="H228" t="s">
+        <v>13</v>
+      </c>
+      <c r="I228" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="229" spans="1:9">
+      <c r="A229" t="s">
+        <v>9</v>
+      </c>
+      <c r="B229" t="s">
+        <v>73</v>
+      </c>
+      <c r="C229" t="s">
+        <v>30</v>
+      </c>
+      <c r="D229" t="s">
+        <v>31</v>
+      </c>
+      <c r="E229">
+        <v>227.5</v>
+      </c>
+      <c r="F229">
+        <v>256.5</v>
+      </c>
+      <c r="G229">
+        <v>12.7</v>
+      </c>
+      <c r="H229">
+        <v>159.5</v>
+      </c>
+      <c r="I229">
+        <v>60.7</v>
+      </c>
+    </row>
+    <row r="230" spans="1:9">
+      <c r="A230" t="s">
+        <v>9</v>
+      </c>
+      <c r="B230" t="s">
+        <v>73</v>
+      </c>
+      <c r="C230" t="s">
+        <v>32</v>
+      </c>
+      <c r="D230" t="s">
+        <v>69</v>
+      </c>
+      <c r="E230">
+        <v>134.3</v>
+      </c>
+      <c r="F230">
+        <v>149.4</v>
+      </c>
+      <c r="G230">
+        <v>11.2</v>
+      </c>
+      <c r="H230" t="s">
+        <v>13</v>
+      </c>
+      <c r="I230" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="231" spans="1:9">
+      <c r="A231" t="s">
+        <v>9</v>
+      </c>
+      <c r="B231" t="s">
+        <v>73</v>
+      </c>
+      <c r="C231" t="s">
+        <v>14</v>
+      </c>
+      <c r="D231" t="s">
+        <v>15</v>
+      </c>
+      <c r="E231">
+        <v>117</v>
+      </c>
+      <c r="F231">
+        <v>130.2</v>
+      </c>
+      <c r="G231">
+        <v>11.2</v>
+      </c>
+      <c r="H231" t="s">
+        <v>13</v>
+      </c>
+      <c r="I231" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="232" spans="1:9">
+      <c r="A232" t="s">
+        <v>9</v>
+      </c>
+      <c r="B232" t="s">
+        <v>73</v>
+      </c>
+      <c r="C232" t="s">
+        <v>32</v>
+      </c>
+      <c r="D232" t="s">
+        <v>33</v>
+      </c>
+      <c r="E232">
+        <v>147.9</v>
+      </c>
+      <c r="F232">
+        <v>163.6</v>
+      </c>
+      <c r="G232">
+        <v>10.6</v>
+      </c>
+      <c r="H232">
+        <v>159.5</v>
+      </c>
+      <c r="I232">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="233" spans="1:9">
+      <c r="A233" t="s">
+        <v>9</v>
+      </c>
+      <c r="B233" t="s">
+        <v>73</v>
+      </c>
+      <c r="C233" t="s">
+        <v>26</v>
+      </c>
+      <c r="D233" t="s">
+        <v>27</v>
+      </c>
+      <c r="E233">
+        <v>141.3</v>
+      </c>
+      <c r="F233">
+        <v>155.9</v>
+      </c>
+      <c r="G233">
+        <v>10.3</v>
+      </c>
+      <c r="H233" t="s">
+        <v>13</v>
+      </c>
+      <c r="I233" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="234" spans="1:9">
+      <c r="A234" t="s">
+        <v>9</v>
+      </c>
+      <c r="B234" t="s">
+        <v>73</v>
+      </c>
+      <c r="C234" t="s">
+        <v>40</v>
+      </c>
+      <c r="D234" t="s">
+        <v>41</v>
+      </c>
+      <c r="E234">
+        <v>216.6</v>
+      </c>
+      <c r="F234">
+        <v>237.2</v>
+      </c>
+      <c r="G234">
+        <v>9.5</v>
+      </c>
+      <c r="H234">
+        <v>159.5</v>
+      </c>
+      <c r="I234">
+        <v>48.7</v>
+      </c>
+    </row>
+    <row r="235" spans="1:9">
+      <c r="A235" t="s">
+        <v>9</v>
+      </c>
+      <c r="B235" t="s">
+        <v>73</v>
+      </c>
+      <c r="C235" t="s">
+        <v>32</v>
+      </c>
+      <c r="D235" t="s">
+        <v>52</v>
+      </c>
+      <c r="E235">
+        <v>220.3</v>
+      </c>
+      <c r="F235">
+        <v>239</v>
+      </c>
+      <c r="G235">
+        <v>8.4</v>
+      </c>
+      <c r="H235">
+        <v>159.5</v>
+      </c>
+      <c r="I235">
+        <v>49.8</v>
+      </c>
+    </row>
+    <row r="236" spans="1:9">
+      <c r="A236" t="s">
+        <v>9</v>
+      </c>
+      <c r="B236" t="s">
+        <v>73</v>
+      </c>
+      <c r="C236" t="s">
+        <v>32</v>
+      </c>
+      <c r="D236" t="s">
+        <v>67</v>
+      </c>
+      <c r="E236">
+        <v>168.1</v>
+      </c>
+      <c r="F236">
+        <v>179.6</v>
+      </c>
+      <c r="G236">
+        <v>6.8</v>
+      </c>
+      <c r="H236">
+        <v>159.5</v>
+      </c>
+      <c r="I236">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="237" spans="1:9">
+      <c r="A237" t="s">
+        <v>9</v>
+      </c>
+      <c r="B237" t="s">
+        <v>73</v>
+      </c>
+      <c r="C237" t="s">
+        <v>16</v>
+      </c>
+      <c r="D237" t="s">
+        <v>56</v>
+      </c>
+      <c r="E237">
+        <v>173.6</v>
+      </c>
+      <c r="F237">
+        <v>180.4</v>
+      </c>
+      <c r="G237">
+        <v>3.9</v>
+      </c>
+      <c r="H237">
+        <v>159.5</v>
+      </c>
+      <c r="I237">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="238" spans="1:9">
+      <c r="A238" t="s">
+        <v>9</v>
+      </c>
+      <c r="B238" t="s">
+        <v>73</v>
+      </c>
+      <c r="C238" t="s">
+        <v>45</v>
+      </c>
+      <c r="D238" t="s">
+        <v>47</v>
+      </c>
+      <c r="E238">
+        <v>178.2</v>
+      </c>
+      <c r="F238">
+        <v>185</v>
+      </c>
+      <c r="G238">
+        <v>3.7</v>
+      </c>
+      <c r="H238">
+        <v>159.5</v>
+      </c>
+      <c r="I238">
+        <v>15.9</v>
+      </c>
+    </row>
+    <row r="239" spans="1:9">
+      <c r="A239" t="s">
+        <v>9</v>
+      </c>
+      <c r="B239" t="s">
+        <v>73</v>
+      </c>
+      <c r="C239" t="s">
+        <v>45</v>
+      </c>
+      <c r="D239" t="s">
+        <v>46</v>
+      </c>
+      <c r="E239">
+        <v>176.6</v>
+      </c>
+      <c r="F239">
+        <v>180.4</v>
+      </c>
+      <c r="G239">
+        <v>2.1</v>
+      </c>
+      <c r="H239">
+        <v>159.5</v>
+      </c>
+      <c r="I239">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="240" spans="1:9">
+      <c r="A240" t="s">
+        <v>9</v>
+      </c>
+      <c r="B240" t="s">
+        <v>73</v>
+      </c>
+      <c r="C240" t="s">
+        <v>48</v>
+      </c>
+      <c r="D240" t="s">
+        <v>50</v>
+      </c>
+      <c r="E240">
+        <v>209.5</v>
+      </c>
+      <c r="F240">
+        <v>209.7</v>
+      </c>
+      <c r="G240">
+        <v>0</v>
+      </c>
+      <c r="H240">
+        <v>159.5</v>
+      </c>
+      <c r="I240">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="241" spans="1:9">
+      <c r="A241" t="s">
+        <v>9</v>
+      </c>
+      <c r="B241" t="s">
+        <v>73</v>
+      </c>
+      <c r="C241" t="s">
+        <v>16</v>
+      </c>
+      <c r="D241" t="s">
+        <v>51</v>
+      </c>
+      <c r="E241">
+        <v>180</v>
+      </c>
+      <c r="F241">
+        <v>178.5</v>
+      </c>
+      <c r="G241">
+        <v>-0.8</v>
+      </c>
+      <c r="H241">
+        <v>159.5</v>
+      </c>
+      <c r="I241">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="242" spans="1:9">
+      <c r="A242" t="s">
+        <v>9</v>
+      </c>
+      <c r="B242" t="s">
+        <v>73</v>
+      </c>
+      <c r="C242" t="s">
+        <v>26</v>
+      </c>
+      <c r="D242" t="s">
+        <v>53</v>
+      </c>
+      <c r="E242">
+        <v>220.1</v>
+      </c>
+      <c r="F242">
+        <v>207.4</v>
+      </c>
+      <c r="G242">
+        <v>-5.7</v>
+      </c>
+      <c r="H242">
+        <v>159.5</v>
+      </c>
+      <c r="I242">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="243" spans="1:9">
+      <c r="A243" t="s">
+        <v>9</v>
+      </c>
+      <c r="B243" t="s">
+        <v>74</v>
+      </c>
+      <c r="C243" t="s">
+        <v>16</v>
+      </c>
+      <c r="D243" t="s">
+        <v>17</v>
+      </c>
+      <c r="E243">
+        <v>151.8</v>
+      </c>
+      <c r="F243">
+        <v>200.3</v>
+      </c>
+      <c r="G243">
+        <v>31.9</v>
+      </c>
+      <c r="H243">
+        <v>159.3</v>
+      </c>
+      <c r="I243">
+        <v>25.7</v>
+      </c>
+    </row>
+    <row r="244" spans="1:9">
+      <c r="A244" t="s">
+        <v>9</v>
+      </c>
+      <c r="B244" t="s">
+        <v>74</v>
+      </c>
+      <c r="C244" t="s">
+        <v>48</v>
+      </c>
+      <c r="D244" t="s">
+        <v>49</v>
+      </c>
+      <c r="E244">
+        <v>184.6</v>
+      </c>
+      <c r="F244">
+        <v>219.3</v>
+      </c>
+      <c r="G244">
+        <v>18.8</v>
+      </c>
+      <c r="H244">
+        <v>159.3</v>
+      </c>
+      <c r="I244">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="245" spans="1:9">
+      <c r="A245" t="s">
+        <v>9</v>
+      </c>
+      <c r="B245" t="s">
+        <v>74</v>
+      </c>
+      <c r="C245" t="s">
+        <v>28</v>
+      </c>
+      <c r="D245" t="s">
+        <v>60</v>
+      </c>
+      <c r="E245">
+        <v>93.6</v>
+      </c>
+      <c r="F245">
+        <v>106.4</v>
+      </c>
+      <c r="G245">
+        <v>13.6</v>
+      </c>
+      <c r="H245" t="s">
+        <v>13</v>
+      </c>
+      <c r="I245" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="246" spans="1:9">
+      <c r="A246" t="s">
+        <v>9</v>
+      </c>
+      <c r="B246" t="s">
+        <v>74</v>
+      </c>
+      <c r="C246" t="s">
+        <v>14</v>
+      </c>
+      <c r="D246" t="s">
+        <v>15</v>
+      </c>
+      <c r="E246">
+        <v>117</v>
+      </c>
+      <c r="F246">
+        <v>132.4</v>
+      </c>
+      <c r="G246">
+        <v>13</v>
+      </c>
+      <c r="H246" t="s">
+        <v>13</v>
+      </c>
+      <c r="I246" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="247" spans="1:9">
+      <c r="A247" t="s">
+        <v>9</v>
+      </c>
+      <c r="B247" t="s">
+        <v>74</v>
+      </c>
+      <c r="C247" t="s">
+        <v>30</v>
+      </c>
+      <c r="D247" t="s">
+        <v>31</v>
+      </c>
+      <c r="E247">
+        <v>227.5</v>
+      </c>
+      <c r="F247">
+        <v>257.1</v>
+      </c>
+      <c r="G247">
+        <v>13</v>
+      </c>
+      <c r="H247">
+        <v>159.3</v>
+      </c>
+      <c r="I247">
+        <v>61.3</v>
+      </c>
+    </row>
+    <row r="248" spans="1:9">
+      <c r="A248" t="s">
+        <v>9</v>
+      </c>
+      <c r="B248" t="s">
+        <v>74</v>
+      </c>
+      <c r="C248" t="s">
+        <v>32</v>
+      </c>
+      <c r="D248" t="s">
+        <v>33</v>
+      </c>
+      <c r="E248">
+        <v>147.9</v>
+      </c>
+      <c r="F248">
+        <v>164.6</v>
+      </c>
+      <c r="G248">
+        <v>11.2</v>
+      </c>
+      <c r="H248">
+        <v>159.3</v>
+      </c>
+      <c r="I248">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="249" spans="1:9">
+      <c r="A249" t="s">
+        <v>9</v>
+      </c>
+      <c r="B249" t="s">
+        <v>74</v>
+      </c>
+      <c r="C249" t="s">
+        <v>32</v>
+      </c>
+      <c r="D249" t="s">
+        <v>69</v>
+      </c>
+      <c r="E249">
+        <v>134.3</v>
+      </c>
+      <c r="F249">
+        <v>148.4</v>
+      </c>
+      <c r="G249">
+        <v>10.5</v>
+      </c>
+      <c r="H249" t="s">
+        <v>13</v>
+      </c>
+      <c r="I249" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="250" spans="1:9">
+      <c r="A250" t="s">
+        <v>9</v>
+      </c>
+      <c r="B250" t="s">
+        <v>74</v>
+      </c>
+      <c r="C250" t="s">
+        <v>26</v>
+      </c>
+      <c r="D250" t="s">
+        <v>27</v>
+      </c>
+      <c r="E250">
+        <v>141.3</v>
+      </c>
+      <c r="F250">
+        <v>156.1</v>
+      </c>
+      <c r="G250">
+        <v>10.4</v>
+      </c>
+      <c r="H250" t="s">
+        <v>13</v>
+      </c>
+      <c r="I250" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="251" spans="1:9">
+      <c r="A251" t="s">
+        <v>9</v>
+      </c>
+      <c r="B251" t="s">
+        <v>74</v>
+      </c>
+      <c r="C251" t="s">
+        <v>40</v>
+      </c>
+      <c r="D251" t="s">
+        <v>41</v>
+      </c>
+      <c r="E251">
+        <v>216.6</v>
+      </c>
+      <c r="F251">
+        <v>236</v>
+      </c>
+      <c r="G251">
+        <v>8.9</v>
+      </c>
+      <c r="H251">
+        <v>159.3</v>
+      </c>
+      <c r="I251">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:9">
+      <c r="A252" t="s">
+        <v>9</v>
+      </c>
+      <c r="B252" t="s">
+        <v>74</v>
+      </c>
+      <c r="C252" t="s">
+        <v>32</v>
+      </c>
+      <c r="D252" t="s">
+        <v>52</v>
+      </c>
+      <c r="E252">
+        <v>220.3</v>
+      </c>
+      <c r="F252">
+        <v>238.4</v>
+      </c>
+      <c r="G252">
+        <v>8.2</v>
+      </c>
+      <c r="H252">
+        <v>159.3</v>
+      </c>
+      <c r="I252">
+        <v>49.5</v>
+      </c>
+    </row>
+    <row r="253" spans="1:9">
+      <c r="A253" t="s">
+        <v>9</v>
+      </c>
+      <c r="B253" t="s">
+        <v>74</v>
+      </c>
+      <c r="C253" t="s">
+        <v>32</v>
+      </c>
+      <c r="D253" t="s">
+        <v>67</v>
+      </c>
+      <c r="E253">
+        <v>168.1</v>
+      </c>
+      <c r="F253">
+        <v>180.4</v>
+      </c>
+      <c r="G253">
+        <v>7.3</v>
+      </c>
+      <c r="H253">
+        <v>159.3</v>
+      </c>
+      <c r="I253">
+        <v>13.1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:9">
+      <c r="A254" t="s">
+        <v>9</v>
+      </c>
+      <c r="B254" t="s">
+        <v>74</v>
+      </c>
+      <c r="C254" t="s">
+        <v>45</v>
+      </c>
+      <c r="D254" t="s">
+        <v>47</v>
+      </c>
+      <c r="E254">
+        <v>178.2</v>
+      </c>
+      <c r="F254">
+        <v>184.4</v>
+      </c>
+      <c r="G254">
+        <v>3.4</v>
+      </c>
+      <c r="H254">
+        <v>159.3</v>
+      </c>
+      <c r="I254">
+        <v>15.7</v>
+      </c>
+    </row>
+    <row r="255" spans="1:9">
+      <c r="A255" t="s">
+        <v>9</v>
+      </c>
+      <c r="B255" t="s">
+        <v>74</v>
+      </c>
+      <c r="C255" t="s">
+        <v>16</v>
+      </c>
+      <c r="D255" t="s">
+        <v>56</v>
+      </c>
+      <c r="E255">
+        <v>173.6</v>
+      </c>
+      <c r="F255">
+        <v>179.6</v>
+      </c>
+      <c r="G255">
+        <v>3.4</v>
+      </c>
+      <c r="H255">
+        <v>159.3</v>
+      </c>
+      <c r="I255">
+        <v>12.7</v>
+      </c>
+    </row>
+    <row r="256" spans="1:9">
+      <c r="A256" t="s">
+        <v>9</v>
+      </c>
+      <c r="B256" t="s">
+        <v>74</v>
+      </c>
+      <c r="C256" t="s">
+        <v>45</v>
+      </c>
+      <c r="D256" t="s">
+        <v>46</v>
+      </c>
+      <c r="E256">
+        <v>176.6</v>
+      </c>
+      <c r="F256">
+        <v>180</v>
+      </c>
+      <c r="G256">
+        <v>1.9</v>
+      </c>
+      <c r="H256">
+        <v>159.3</v>
+      </c>
+      <c r="I256">
+        <v>12.9</v>
+      </c>
+    </row>
+    <row r="257" spans="1:9">
+      <c r="A257" t="s">
+        <v>9</v>
+      </c>
+      <c r="B257" t="s">
+        <v>74</v>
+      </c>
+      <c r="C257" t="s">
+        <v>48</v>
+      </c>
+      <c r="D257" t="s">
+        <v>50</v>
+      </c>
+      <c r="E257">
+        <v>209.5</v>
+      </c>
+      <c r="F257">
+        <v>209.5</v>
+      </c>
+      <c r="G257">
+        <v>0</v>
+      </c>
+      <c r="H257">
+        <v>159.3</v>
+      </c>
+      <c r="I257">
+        <v>31.4</v>
+      </c>
+    </row>
+    <row r="258" spans="1:9">
+      <c r="A258" t="s">
+        <v>9</v>
+      </c>
+      <c r="B258" t="s">
+        <v>74</v>
+      </c>
+      <c r="C258" t="s">
+        <v>16</v>
+      </c>
+      <c r="D258" t="s">
+        <v>51</v>
+      </c>
+      <c r="E258">
+        <v>180</v>
+      </c>
+      <c r="F258">
+        <v>177.9</v>
+      </c>
+      <c r="G258">
+        <v>-1.1</v>
+      </c>
+      <c r="H258">
+        <v>159.3</v>
+      </c>
+      <c r="I258">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="259" spans="1:9">
+      <c r="A259" t="s">
+        <v>9</v>
+      </c>
+      <c r="B259" t="s">
+        <v>74</v>
+      </c>
+      <c r="C259" t="s">
+        <v>26</v>
+      </c>
+      <c r="D259" t="s">
+        <v>53</v>
+      </c>
+      <c r="E259">
+        <v>220.1</v>
+      </c>
+      <c r="F259">
+        <v>207.8</v>
+      </c>
+      <c r="G259">
+        <v>-5.5</v>
+      </c>
+      <c r="H259">
+        <v>159.3</v>
+      </c>
+      <c r="I259">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="260" spans="1:9">
+      <c r="A260" t="s">
+        <v>9</v>
+      </c>
+      <c r="B260" t="s">
+        <v>75</v>
+      </c>
+      <c r="C260" t="s">
+        <v>16</v>
+      </c>
+      <c r="D260" t="s">
+        <v>17</v>
+      </c>
+      <c r="E260">
+        <v>151.8</v>
+      </c>
+      <c r="F260">
+        <v>199.5</v>
+      </c>
+      <c r="G260">
+        <v>31.3</v>
+      </c>
+      <c r="H260">
+        <v>159</v>
+      </c>
+      <c r="I260">
+        <v>25.4</v>
+      </c>
+    </row>
+    <row r="261" spans="1:9">
+      <c r="A261" t="s">
+        <v>9</v>
+      </c>
+      <c r="B261" t="s">
+        <v>75</v>
+      </c>
+      <c r="C261" t="s">
+        <v>14</v>
+      </c>
+      <c r="D261" t="s">
+        <v>15</v>
+      </c>
+      <c r="E261">
+        <v>117</v>
+      </c>
+      <c r="F261">
+        <v>133.6</v>
+      </c>
+      <c r="G261">
+        <v>14.1</v>
+      </c>
+      <c r="H261" t="s">
+        <v>13</v>
+      </c>
+      <c r="I261" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="262" spans="1:9">
+      <c r="A262" t="s">
+        <v>9</v>
+      </c>
+      <c r="B262" t="s">
+        <v>75</v>
+      </c>
+      <c r="C262" t="s">
+        <v>30</v>
+      </c>
+      <c r="D262" t="s">
+        <v>31</v>
+      </c>
+      <c r="E262">
+        <v>227.5</v>
+      </c>
+      <c r="F262">
+        <v>257.7</v>
+      </c>
+      <c r="G262">
+        <v>13.2</v>
+      </c>
+      <c r="H262">
+        <v>159</v>
+      </c>
+      <c r="I262">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="263" spans="1:9">
+      <c r="A263" t="s">
+        <v>9</v>
+      </c>
+      <c r="B263" t="s">
+        <v>75</v>
+      </c>
+      <c r="C263" t="s">
+        <v>28</v>
+      </c>
+      <c r="D263" t="s">
+        <v>60</v>
+      </c>
+      <c r="E263">
+        <v>93.6</v>
+      </c>
+      <c r="F263">
+        <v>105.5</v>
+      </c>
+      <c r="G263">
+        <v>12.6</v>
+      </c>
+      <c r="H263" t="s">
+        <v>13</v>
+      </c>
+      <c r="I263" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="264" spans="1:9">
+      <c r="A264" t="s">
+        <v>9</v>
+      </c>
+      <c r="B264" t="s">
+        <v>75</v>
+      </c>
+      <c r="C264" t="s">
+        <v>48</v>
+      </c>
+      <c r="D264" t="s">
+        <v>49</v>
+      </c>
+      <c r="E264">
+        <v>198.6</v>
+      </c>
+      <c r="F264">
+        <v>219.4</v>
+      </c>
+      <c r="G264">
+        <v>10.4</v>
+      </c>
+      <c r="H264">
+        <v>159</v>
+      </c>
+      <c r="I264">
+        <v>37.9</v>
+      </c>
+    </row>
+    <row r="265" spans="1:9">
+      <c r="A265" t="s">
+        <v>9</v>
+      </c>
+      <c r="B265" t="s">
+        <v>75</v>
+      </c>
+      <c r="C265" t="s">
+        <v>40</v>
+      </c>
+      <c r="D265" t="s">
+        <v>41</v>
+      </c>
+      <c r="E265">
+        <v>216.6</v>
+      </c>
+      <c r="F265">
+        <v>235.6</v>
+      </c>
+      <c r="G265">
+        <v>8.7</v>
+      </c>
+      <c r="H265">
+        <v>159</v>
+      </c>
+      <c r="I265">
+        <v>48.1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:9">
+      <c r="A266" t="s">
+        <v>9</v>
+      </c>
+      <c r="B266" t="s">
+        <v>75</v>
+      </c>
+      <c r="C266" t="s">
+        <v>32</v>
+      </c>
+      <c r="D266" t="s">
+        <v>52</v>
+      </c>
+      <c r="E266">
+        <v>220.3</v>
+      </c>
+      <c r="F266">
+        <v>236.9</v>
+      </c>
+      <c r="G266">
+        <v>7.5</v>
+      </c>
+      <c r="H266">
+        <v>159</v>
+      </c>
+      <c r="I266">
+        <v>48.9</v>
+      </c>
+    </row>
+    <row r="267" spans="1:9">
+      <c r="A267" t="s">
+        <v>9</v>
+      </c>
+      <c r="B267" t="s">
+        <v>75</v>
+      </c>
+      <c r="C267" t="s">
+        <v>32</v>
+      </c>
+      <c r="D267" t="s">
+        <v>67</v>
+      </c>
+      <c r="E267">
+        <v>168.1</v>
+      </c>
+      <c r="F267">
+        <v>180.6</v>
+      </c>
+      <c r="G267">
+        <v>7.4</v>
+      </c>
+      <c r="H267">
+        <v>159</v>
+      </c>
+      <c r="I267">
+        <v>13.5</v>
+      </c>
+    </row>
+    <row r="268" spans="1:9">
+      <c r="A268" t="s">
+        <v>9</v>
+      </c>
+      <c r="B268" t="s">
+        <v>75</v>
+      </c>
+      <c r="C268" t="s">
+        <v>45</v>
+      </c>
+      <c r="D268" t="s">
+        <v>47</v>
+      </c>
+      <c r="E268">
+        <v>178.2</v>
+      </c>
+      <c r="F268">
+        <v>183.8</v>
+      </c>
+      <c r="G268">
+        <v>3.1</v>
+      </c>
+      <c r="H268">
+        <v>159</v>
+      </c>
+      <c r="I268">
+        <v>15.5</v>
+      </c>
+    </row>
+    <row r="269" spans="1:9">
+      <c r="A269" t="s">
+        <v>9</v>
+      </c>
+      <c r="B269" t="s">
+        <v>75</v>
+      </c>
+      <c r="C269" t="s">
+        <v>16</v>
+      </c>
+      <c r="D269" t="s">
+        <v>56</v>
+      </c>
+      <c r="E269">
+        <v>173.6</v>
+      </c>
+      <c r="F269">
+        <v>178.5</v>
+      </c>
+      <c r="G269">
+        <v>2.8</v>
+      </c>
+      <c r="H269">
+        <v>159</v>
+      </c>
+      <c r="I269">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="270" spans="1:9">
+      <c r="A270" t="s">
+        <v>9</v>
+      </c>
+      <c r="B270" t="s">
+        <v>75</v>
+      </c>
+      <c r="C270" t="s">
+        <v>45</v>
+      </c>
+      <c r="D270" t="s">
+        <v>46</v>
+      </c>
+      <c r="E270">
+        <v>176.6</v>
+      </c>
+      <c r="F270">
+        <v>180.1</v>
+      </c>
+      <c r="G270">
+        <v>1.9</v>
+      </c>
+      <c r="H270">
+        <v>159</v>
+      </c>
+      <c r="I270">
+        <v>13.2</v>
+      </c>
+    </row>
+    <row r="271" spans="1:9">
+      <c r="A271" t="s">
+        <v>9</v>
+      </c>
+      <c r="B271" t="s">
+        <v>75</v>
+      </c>
+      <c r="C271" t="s">
+        <v>48</v>
+      </c>
+      <c r="D271" t="s">
+        <v>50</v>
+      </c>
+      <c r="E271">
+        <v>209.5</v>
+      </c>
+      <c r="F271">
+        <v>209.5</v>
+      </c>
+      <c r="G271">
+        <v>0</v>
+      </c>
+      <c r="H271">
+        <v>159</v>
+      </c>
+      <c r="I271">
+        <v>31.7</v>
+      </c>
+    </row>
+    <row r="272" spans="1:9">
+      <c r="A272" t="s">
+        <v>9</v>
+      </c>
+      <c r="B272" t="s">
+        <v>75</v>
+      </c>
+      <c r="C272" t="s">
+        <v>16</v>
+      </c>
+      <c r="D272" t="s">
+        <v>51</v>
+      </c>
+      <c r="E272">
+        <v>180</v>
+      </c>
+      <c r="F272">
+        <v>176.9</v>
+      </c>
+      <c r="G272">
+        <v>-1.7</v>
+      </c>
+      <c r="H272">
+        <v>159</v>
+      </c>
+      <c r="I272">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="273" spans="1:9">
+      <c r="A273" t="s">
+        <v>9</v>
+      </c>
+      <c r="B273" t="s">
+        <v>75</v>
+      </c>
+      <c r="C273" t="s">
+        <v>26</v>
+      </c>
+      <c r="D273" t="s">
+        <v>53</v>
+      </c>
+      <c r="E273">
+        <v>220.1</v>
+      </c>
+      <c r="F273">
+        <v>208.1</v>
+      </c>
+      <c r="G273">
+        <v>-5.4</v>
+      </c>
+      <c r="H273">
+        <v>159</v>
+      </c>
+      <c r="I273">
+        <v>30.8</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H127" etc:filterBottomFollowUsedRange="0">
+  <autoFilter xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData" ref="A1:H168" etc:filterBottomFollowUsedRange="0">
     <extLst/>
   </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/source/8、绩效异常岗位/2、卸车岗/卸车岗-6月.xlsx
+++ b/source/8、绩效异常岗位/2、卸车岗/卸车岗-6月.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I371"/>
+  <dimension ref="A1:I480"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14513,6 +14513,4187 @@
         <v>31</v>
       </c>
     </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D372" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="E372" t="n">
+        <v>151.8</v>
+      </c>
+      <c r="F372" t="n">
+        <v>199.6</v>
+      </c>
+      <c r="G372" t="n">
+        <v>31.4</v>
+      </c>
+      <c r="H372" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="I372" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D373" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E373" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F373" t="n">
+        <v>130.4</v>
+      </c>
+      <c r="G373" t="n">
+        <v>16.9</v>
+      </c>
+      <c r="H373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I373" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D374" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E374" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="F374" t="n">
+        <v>143.4</v>
+      </c>
+      <c r="G374" t="n">
+        <v>15</v>
+      </c>
+      <c r="H374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I374" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E375" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F375" t="n">
+        <v>121.7</v>
+      </c>
+      <c r="G375" t="n">
+        <v>15</v>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I375" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E376" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="F376" t="n">
+        <v>259.9</v>
+      </c>
+      <c r="G376" t="n">
+        <v>14.2</v>
+      </c>
+      <c r="H376" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="I376" t="n">
+        <v>62.7</v>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>天津区</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E377" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F377" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="G377" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I377" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>长治</t>
+        </is>
+      </c>
+      <c r="E378" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F378" t="n">
+        <v>104.5</v>
+      </c>
+      <c r="G378" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E379" t="n">
+        <v>117</v>
+      </c>
+      <c r="F379" t="n">
+        <v>130</v>
+      </c>
+      <c r="G379" t="n">
+        <v>11</v>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I379" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E380" t="n">
+        <v>198.6</v>
+      </c>
+      <c r="F380" t="n">
+        <v>218.9</v>
+      </c>
+      <c r="G380" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H380" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="I380" t="n">
+        <v>37.1</v>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>常德</t>
+        </is>
+      </c>
+      <c r="E381" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="F381" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="G381" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I381" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>揭阳</t>
+        </is>
+      </c>
+      <c r="E382" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="F382" t="n">
+        <v>234.9</v>
+      </c>
+      <c r="G382" t="n">
+        <v>8.4</v>
+      </c>
+      <c r="H382" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="I382" t="n">
+        <v>47.1</v>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D383" t="inlineStr">
+        <is>
+          <t>菏泽</t>
+        </is>
+      </c>
+      <c r="E383" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="F383" t="n">
+        <v>179.6</v>
+      </c>
+      <c r="G383" t="n">
+        <v>6.8</v>
+      </c>
+      <c r="H383" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="I383" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D384" t="inlineStr">
+        <is>
+          <t>临沂</t>
+        </is>
+      </c>
+      <c r="E384" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="F384" t="n">
+        <v>232.4</v>
+      </c>
+      <c r="G384" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="H384" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="I384" t="n">
+        <v>45.5</v>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D385" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E385" t="n">
+        <v>173.6</v>
+      </c>
+      <c r="F385" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="G385" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="H385" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="I385" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D386" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E386" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="F386" t="n">
+        <v>178.4</v>
+      </c>
+      <c r="G386" t="n">
+        <v>1</v>
+      </c>
+      <c r="H386" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="I386" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D387" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E387" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="F387" t="n">
+        <v>210.8</v>
+      </c>
+      <c r="G387" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H387" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="I387" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D388" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E388" t="n">
+        <v>180</v>
+      </c>
+      <c r="F388" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="G388" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="H388" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="I388" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D389" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E389" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="F389" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="G389" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H389" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="I389" t="n">
+        <v>10.1</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>2026-06-21</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E390" t="n">
+        <v>220.1</v>
+      </c>
+      <c r="F390" t="n">
+        <v>208.5</v>
+      </c>
+      <c r="G390" t="n">
+        <v>-5.3</v>
+      </c>
+      <c r="H390" t="n">
+        <v>159.6</v>
+      </c>
+      <c r="I390" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="E391" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="F391" t="n">
+        <v>198.6</v>
+      </c>
+      <c r="G391" t="n">
+        <v>17.4</v>
+      </c>
+      <c r="H391" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="I391" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E392" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F392" t="n">
+        <v>129.9</v>
+      </c>
+      <c r="G392" t="n">
+        <v>16.5</v>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E393" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F393" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="G393" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E394" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="F394" t="n">
+        <v>142.7</v>
+      </c>
+      <c r="G394" t="n">
+        <v>14.5</v>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E395" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="F395" t="n">
+        <v>258.6</v>
+      </c>
+      <c r="G395" t="n">
+        <v>13.6</v>
+      </c>
+      <c r="H395" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="I395" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>天津区</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E396" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F396" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="G396" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr">
+        <is>
+          <t>长治</t>
+        </is>
+      </c>
+      <c r="E397" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F397" t="n">
+        <v>104.8</v>
+      </c>
+      <c r="G397" t="n">
+        <v>11.9</v>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>宁夏区</t>
+        </is>
+      </c>
+      <c r="D398" t="inlineStr">
+        <is>
+          <t>银川</t>
+        </is>
+      </c>
+      <c r="E398" t="n">
+        <v>117</v>
+      </c>
+      <c r="F398" t="n">
+        <v>130</v>
+      </c>
+      <c r="G398" t="n">
+        <v>11</v>
+      </c>
+      <c r="H398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I398" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D399" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E399" t="n">
+        <v>198.6</v>
+      </c>
+      <c r="F399" t="n">
+        <v>218.8</v>
+      </c>
+      <c r="G399" t="n">
+        <v>10.2</v>
+      </c>
+      <c r="H399" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="I399" t="n">
+        <v>37.5</v>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D400" t="inlineStr">
+        <is>
+          <t>常德</t>
+        </is>
+      </c>
+      <c r="E400" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="F400" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="G400" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I400" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+      <c r="D401" t="inlineStr">
+        <is>
+          <t>揭阳</t>
+        </is>
+      </c>
+      <c r="E401" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="F401" t="n">
+        <v>234.6</v>
+      </c>
+      <c r="G401" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="H401" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="I401" t="n">
+        <v>47.5</v>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D402" t="inlineStr">
+        <is>
+          <t>菏泽</t>
+        </is>
+      </c>
+      <c r="E402" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="F402" t="n">
+        <v>178.9</v>
+      </c>
+      <c r="G402" t="n">
+        <v>6.4</v>
+      </c>
+      <c r="H402" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="I402" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D403" t="inlineStr">
+        <is>
+          <t>临沂</t>
+        </is>
+      </c>
+      <c r="E403" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="F403" t="n">
+        <v>231.7</v>
+      </c>
+      <c r="G403" t="n">
+        <v>5.1</v>
+      </c>
+      <c r="H403" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="I403" t="n">
+        <v>45.6</v>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D404" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E404" t="n">
+        <v>173.6</v>
+      </c>
+      <c r="F404" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="G404" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H404" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="I404" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D405" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E405" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="F405" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="G405" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H405" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="I405" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D406" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E406" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="F406" t="n">
+        <v>210.3</v>
+      </c>
+      <c r="G406" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H406" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="I406" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D407" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E407" t="n">
+        <v>180</v>
+      </c>
+      <c r="F407" t="n">
+        <v>178.2</v>
+      </c>
+      <c r="G407" t="n">
+        <v>-0.9</v>
+      </c>
+      <c r="H407" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="I407" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D408" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E408" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="F408" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="G408" t="n">
+        <v>-4.5</v>
+      </c>
+      <c r="H408" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="I408" t="n">
+        <v>10.5</v>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>2026-06-22</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D409" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E409" t="n">
+        <v>220.1</v>
+      </c>
+      <c r="F409" t="n">
+        <v>207.9</v>
+      </c>
+      <c r="G409" t="n">
+        <v>-5.5</v>
+      </c>
+      <c r="H409" t="n">
+        <v>159.1</v>
+      </c>
+      <c r="I409" t="n">
+        <v>30.7</v>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D410" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="E410" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="F410" t="n">
+        <v>198</v>
+      </c>
+      <c r="G410" t="n">
+        <v>17</v>
+      </c>
+      <c r="H410" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I410" t="n">
+        <v>24.6</v>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D411" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E411" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F411" t="n">
+        <v>129.7</v>
+      </c>
+      <c r="G411" t="n">
+        <v>16.3</v>
+      </c>
+      <c r="H411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I411" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D412" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E412" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F412" t="n">
+        <v>121.9</v>
+      </c>
+      <c r="G412" t="n">
+        <v>15.1</v>
+      </c>
+      <c r="H412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I412" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D413" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E413" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="F413" t="n">
+        <v>142</v>
+      </c>
+      <c r="G413" t="n">
+        <v>13.9</v>
+      </c>
+      <c r="H413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I413" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="414">
+      <c r="A414" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B414" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C414" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D414" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E414" t="n">
+        <v>227.5</v>
+      </c>
+      <c r="F414" t="n">
+        <v>258.2</v>
+      </c>
+      <c r="G414" t="n">
+        <v>13.4</v>
+      </c>
+      <c r="H414" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I414" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="415">
+      <c r="A415" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B415" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C415" t="inlineStr">
+        <is>
+          <t>天津区</t>
+        </is>
+      </c>
+      <c r="D415" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E415" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F415" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="G415" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I415" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="416">
+      <c r="A416" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B416" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C416" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D416" t="inlineStr">
+        <is>
+          <t>长治</t>
+        </is>
+      </c>
+      <c r="E416" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F416" t="n">
+        <v>104.6</v>
+      </c>
+      <c r="G416" t="n">
+        <v>11.6</v>
+      </c>
+      <c r="H416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I416" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="417">
+      <c r="A417" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B417" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C417" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D417" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E417" t="n">
+        <v>198.6</v>
+      </c>
+      <c r="F417" t="n">
+        <v>218.5</v>
+      </c>
+      <c r="G417" t="n">
+        <v>10</v>
+      </c>
+      <c r="H417" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I417" t="n">
+        <v>37.6</v>
+      </c>
+    </row>
+    <row r="418">
+      <c r="A418" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B418" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C418" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D418" t="inlineStr">
+        <is>
+          <t>常德</t>
+        </is>
+      </c>
+      <c r="E418" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="F418" t="n">
+        <v>128.3</v>
+      </c>
+      <c r="G418" t="n">
+        <v>10</v>
+      </c>
+      <c r="H418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I418" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="419">
+      <c r="A419" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B419" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C419" t="inlineStr">
+        <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+      <c r="D419" t="inlineStr">
+        <is>
+          <t>揭阳</t>
+        </is>
+      </c>
+      <c r="E419" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="F419" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="G419" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H419" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I419" t="n">
+        <v>47.6</v>
+      </c>
+    </row>
+    <row r="420">
+      <c r="A420" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B420" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C420" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D420" t="inlineStr">
+        <is>
+          <t>菏泽</t>
+        </is>
+      </c>
+      <c r="E420" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="F420" t="n">
+        <v>178.7</v>
+      </c>
+      <c r="G420" t="n">
+        <v>6.2</v>
+      </c>
+      <c r="H420" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I420" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="421">
+      <c r="A421" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B421" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C421" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D421" t="inlineStr">
+        <is>
+          <t>临沂</t>
+        </is>
+      </c>
+      <c r="E421" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="F421" t="n">
+        <v>231.5</v>
+      </c>
+      <c r="G421" t="n">
+        <v>5</v>
+      </c>
+      <c r="H421" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I421" t="n">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="422">
+      <c r="A422" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B422" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C422" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D422" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E422" t="n">
+        <v>173.6</v>
+      </c>
+      <c r="F422" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="G422" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="H422" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I422" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="423">
+      <c r="A423" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B423" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C423" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D423" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E423" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="F423" t="n">
+        <v>177.8</v>
+      </c>
+      <c r="G423" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="H423" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I423" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="424">
+      <c r="A424" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B424" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C424" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D424" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E424" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="F424" t="n">
+        <v>210.2</v>
+      </c>
+      <c r="G424" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H424" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I424" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="425">
+      <c r="A425" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B425" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C425" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D425" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E425" t="n">
+        <v>180</v>
+      </c>
+      <c r="F425" t="n">
+        <v>177.7</v>
+      </c>
+      <c r="G425" t="n">
+        <v>-1.2</v>
+      </c>
+      <c r="H425" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I425" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="426">
+      <c r="A426" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B426" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C426" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D426" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E426" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="F426" t="n">
+        <v>175.9</v>
+      </c>
+      <c r="G426" t="n">
+        <v>-4.4</v>
+      </c>
+      <c r="H426" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I426" t="n">
+        <v>10.7</v>
+      </c>
+    </row>
+    <row r="427">
+      <c r="A427" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B427" t="inlineStr">
+        <is>
+          <t>2026-06-23</t>
+        </is>
+      </c>
+      <c r="C427" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D427" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E427" t="n">
+        <v>220.1</v>
+      </c>
+      <c r="F427" t="n">
+        <v>207.1</v>
+      </c>
+      <c r="G427" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="H427" t="n">
+        <v>158.8</v>
+      </c>
+      <c r="I427" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="428">
+      <c r="A428" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B428" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C428" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D428" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E428" t="n">
+        <v>205.9</v>
+      </c>
+      <c r="F428" t="n">
+        <v>257.7</v>
+      </c>
+      <c r="G428" t="n">
+        <v>25.1</v>
+      </c>
+      <c r="H428" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I428" t="n">
+        <v>62.5</v>
+      </c>
+    </row>
+    <row r="429">
+      <c r="A429" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B429" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C429" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D429" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="E429" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="F429" t="n">
+        <v>197.8</v>
+      </c>
+      <c r="G429" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H429" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I429" t="n">
+        <v>24.7</v>
+      </c>
+    </row>
+    <row r="430">
+      <c r="A430" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B430" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C430" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D430" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E430" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F430" t="n">
+        <v>129.3</v>
+      </c>
+      <c r="G430" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I430" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="431">
+      <c r="A431" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B431" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C431" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D431" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E431" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F431" t="n">
+        <v>122</v>
+      </c>
+      <c r="G431" t="n">
+        <v>15.3</v>
+      </c>
+      <c r="H431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I431" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="432">
+      <c r="A432" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B432" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C432" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D432" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E432" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="F432" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="G432" t="n">
+        <v>13.5</v>
+      </c>
+      <c r="H432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I432" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="433">
+      <c r="A433" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B433" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C433" t="inlineStr">
+        <is>
+          <t>天津区</t>
+        </is>
+      </c>
+      <c r="D433" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E433" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F433" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="G433" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I433" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="434">
+      <c r="A434" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B434" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C434" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D434" t="inlineStr">
+        <is>
+          <t>长治</t>
+        </is>
+      </c>
+      <c r="E434" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F434" t="n">
+        <v>104</v>
+      </c>
+      <c r="G434" t="n">
+        <v>11</v>
+      </c>
+      <c r="H434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I434" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="435">
+      <c r="A435" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B435" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C435" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D435" t="inlineStr">
+        <is>
+          <t>常德</t>
+        </is>
+      </c>
+      <c r="E435" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="F435" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="G435" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I435" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="436">
+      <c r="A436" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B436" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C436" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D436" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E436" t="n">
+        <v>198.6</v>
+      </c>
+      <c r="F436" t="n">
+        <v>218.5</v>
+      </c>
+      <c r="G436" t="n">
+        <v>10</v>
+      </c>
+      <c r="H436" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I436" t="n">
+        <v>37.8</v>
+      </c>
+    </row>
+    <row r="437">
+      <c r="A437" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B437" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C437" t="inlineStr">
+        <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+      <c r="D437" t="inlineStr">
+        <is>
+          <t>揭阳</t>
+        </is>
+      </c>
+      <c r="E437" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="F437" t="n">
+        <v>234.5</v>
+      </c>
+      <c r="G437" t="n">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="H437" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I437" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="438">
+      <c r="A438" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B438" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C438" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D438" t="inlineStr">
+        <is>
+          <t>菏泽</t>
+        </is>
+      </c>
+      <c r="E438" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="F438" t="n">
+        <v>178.3</v>
+      </c>
+      <c r="G438" t="n">
+        <v>6</v>
+      </c>
+      <c r="H438" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I438" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="439">
+      <c r="A439" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B439" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C439" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D439" t="inlineStr">
+        <is>
+          <t>临沂</t>
+        </is>
+      </c>
+      <c r="E439" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="F439" t="n">
+        <v>231.2</v>
+      </c>
+      <c r="G439" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="H439" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I439" t="n">
+        <v>45.8</v>
+      </c>
+    </row>
+    <row r="440">
+      <c r="A440" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B440" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C440" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D440" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E440" t="n">
+        <v>173.6</v>
+      </c>
+      <c r="F440" t="n">
+        <v>176.2</v>
+      </c>
+      <c r="G440" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H440" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I440" t="n">
+        <v>11.1</v>
+      </c>
+    </row>
+    <row r="441">
+      <c r="A441" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B441" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C441" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D441" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E441" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="F441" t="n">
+        <v>177.7</v>
+      </c>
+      <c r="G441" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="H441" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I441" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="442">
+      <c r="A442" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B442" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C442" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D442" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E442" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="F442" t="n">
+        <v>209.7</v>
+      </c>
+      <c r="G442" t="n">
+        <v>0</v>
+      </c>
+      <c r="H442" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I442" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="443">
+      <c r="A443" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B443" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C443" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D443" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E443" t="n">
+        <v>180</v>
+      </c>
+      <c r="F443" t="n">
+        <v>177.4</v>
+      </c>
+      <c r="G443" t="n">
+        <v>-1.4</v>
+      </c>
+      <c r="H443" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I443" t="n">
+        <v>11.8</v>
+      </c>
+    </row>
+    <row r="444">
+      <c r="A444" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B444" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C444" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D444" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E444" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="F444" t="n">
+        <v>176.7</v>
+      </c>
+      <c r="G444" t="n">
+        <v>-4</v>
+      </c>
+      <c r="H444" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I444" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="445">
+      <c r="A445" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B445" t="inlineStr">
+        <is>
+          <t>2026-06-24</t>
+        </is>
+      </c>
+      <c r="C445" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D445" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E445" t="n">
+        <v>220.1</v>
+      </c>
+      <c r="F445" t="n">
+        <v>206.8</v>
+      </c>
+      <c r="G445" t="n">
+        <v>-6</v>
+      </c>
+      <c r="H445" t="n">
+        <v>158.5</v>
+      </c>
+      <c r="I445" t="n">
+        <v>30.4</v>
+      </c>
+    </row>
+    <row r="446">
+      <c r="A446" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B446" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C446" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D446" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E446" t="n">
+        <v>205.9</v>
+      </c>
+      <c r="F446" t="n">
+        <v>256.8</v>
+      </c>
+      <c r="G446" t="n">
+        <v>24.6</v>
+      </c>
+      <c r="H446" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="I446" t="n">
+        <v>62.1</v>
+      </c>
+    </row>
+    <row r="447">
+      <c r="A447" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B447" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C447" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D447" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="E447" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="F447" t="n">
+        <v>197.7</v>
+      </c>
+      <c r="G447" t="n">
+        <v>16.8</v>
+      </c>
+      <c r="H447" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="I447" t="n">
+        <v>24.8</v>
+      </c>
+    </row>
+    <row r="448">
+      <c r="A448" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B448" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C448" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D448" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E448" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F448" t="n">
+        <v>122.7</v>
+      </c>
+      <c r="G448" t="n">
+        <v>15.9</v>
+      </c>
+      <c r="H448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I448" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="449">
+      <c r="A449" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B449" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C449" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D449" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E449" t="n">
+        <v>111.5</v>
+      </c>
+      <c r="F449" t="n">
+        <v>128.5</v>
+      </c>
+      <c r="G449" t="n">
+        <v>15.2</v>
+      </c>
+      <c r="H449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I449" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="450">
+      <c r="A450" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B450" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C450" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D450" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E450" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="F450" t="n">
+        <v>140.8</v>
+      </c>
+      <c r="G450" t="n">
+        <v>12.9</v>
+      </c>
+      <c r="H450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I450" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>天津区</t>
+        </is>
+      </c>
+      <c r="D451" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E451" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F451" t="n">
+        <v>150.9</v>
+      </c>
+      <c r="G451" t="n">
+        <v>12.1</v>
+      </c>
+      <c r="H451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I451" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D452" t="inlineStr">
+        <is>
+          <t>长治</t>
+        </is>
+      </c>
+      <c r="E452" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F452" t="n">
+        <v>103.8</v>
+      </c>
+      <c r="G452" t="n">
+        <v>10.9</v>
+      </c>
+      <c r="H452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I452" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>湖南区</t>
+        </is>
+      </c>
+      <c r="D453" t="inlineStr">
+        <is>
+          <t>常德</t>
+        </is>
+      </c>
+      <c r="E453" t="n">
+        <v>116.6</v>
+      </c>
+      <c r="F453" t="n">
+        <v>129.1</v>
+      </c>
+      <c r="G453" t="n">
+        <v>10.7</v>
+      </c>
+      <c r="H453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I453" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D454" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E454" t="n">
+        <v>198.6</v>
+      </c>
+      <c r="F454" t="n">
+        <v>218.4</v>
+      </c>
+      <c r="G454" t="n">
+        <v>9.9</v>
+      </c>
+      <c r="H454" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="I454" t="n">
+        <v>37.9</v>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+      <c r="D455" t="inlineStr">
+        <is>
+          <t>揭阳</t>
+        </is>
+      </c>
+      <c r="E455" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="F455" t="n">
+        <v>234.2</v>
+      </c>
+      <c r="G455" t="n">
+        <v>8.1</v>
+      </c>
+      <c r="H455" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="I455" t="n">
+        <v>47.9</v>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D456" t="inlineStr">
+        <is>
+          <t>菏泽</t>
+        </is>
+      </c>
+      <c r="E456" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="F456" t="n">
+        <v>177.7</v>
+      </c>
+      <c r="G456" t="n">
+        <v>5.7</v>
+      </c>
+      <c r="H456" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="I456" t="n">
+        <v>12.2</v>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D457" t="inlineStr">
+        <is>
+          <t>临沂</t>
+        </is>
+      </c>
+      <c r="E457" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="F457" t="n">
+        <v>230.7</v>
+      </c>
+      <c r="G457" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H457" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="I457" t="n">
+        <v>45.7</v>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D458" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E458" t="n">
+        <v>173.6</v>
+      </c>
+      <c r="F458" t="n">
+        <v>175.7</v>
+      </c>
+      <c r="G458" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H458" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="I458" t="n">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D459" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E459" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="F459" t="n">
+        <v>178</v>
+      </c>
+      <c r="G459" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H459" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="I459" t="n">
+        <v>12.4</v>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D460" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E460" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="F460" t="n">
+        <v>209.4</v>
+      </c>
+      <c r="G460" t="n">
+        <v>0</v>
+      </c>
+      <c r="H460" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="I460" t="n">
+        <v>32.2</v>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D461" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E461" t="n">
+        <v>180</v>
+      </c>
+      <c r="F461" t="n">
+        <v>176.9</v>
+      </c>
+      <c r="G461" t="n">
+        <v>-1.7</v>
+      </c>
+      <c r="H461" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="I461" t="n">
+        <v>11.7</v>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D462" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E462" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="F462" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="G462" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="H462" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="I462" t="n">
+        <v>11.4</v>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>2026-06-25</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D463" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E463" t="n">
+        <v>220.1</v>
+      </c>
+      <c r="F463" t="n">
+        <v>206.7</v>
+      </c>
+      <c r="G463" t="n">
+        <v>-6.1</v>
+      </c>
+      <c r="H463" t="n">
+        <v>158.3</v>
+      </c>
+      <c r="I463" t="n">
+        <v>30.5</v>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>浙南区</t>
+        </is>
+      </c>
+      <c r="D464" t="inlineStr">
+        <is>
+          <t>义乌</t>
+        </is>
+      </c>
+      <c r="E464" t="n">
+        <v>205.9</v>
+      </c>
+      <c r="F464" t="n">
+        <v>256</v>
+      </c>
+      <c r="G464" t="n">
+        <v>24.3</v>
+      </c>
+      <c r="H464" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="I464" t="n">
+        <v>61.9</v>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>内蒙古区</t>
+        </is>
+      </c>
+      <c r="D465" t="inlineStr">
+        <is>
+          <t>呼和浩特</t>
+        </is>
+      </c>
+      <c r="E465" t="n">
+        <v>105.8</v>
+      </c>
+      <c r="F465" t="n">
+        <v>123.8</v>
+      </c>
+      <c r="G465" t="n">
+        <v>17</v>
+      </c>
+      <c r="H465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I465" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D466" t="inlineStr">
+        <is>
+          <t>东莞</t>
+        </is>
+      </c>
+      <c r="E466" t="n">
+        <v>169.2</v>
+      </c>
+      <c r="F466" t="n">
+        <v>197.5</v>
+      </c>
+      <c r="G466" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="H466" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="I466" t="n">
+        <v>24.9</v>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D467" t="inlineStr">
+        <is>
+          <t>济南</t>
+        </is>
+      </c>
+      <c r="E467" t="n">
+        <v>124.6</v>
+      </c>
+      <c r="F467" t="n">
+        <v>140.4</v>
+      </c>
+      <c r="G467" t="n">
+        <v>12.6</v>
+      </c>
+      <c r="H467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I467" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>天津区</t>
+        </is>
+      </c>
+      <c r="D468" t="inlineStr">
+        <is>
+          <t>天津</t>
+        </is>
+      </c>
+      <c r="E468" t="n">
+        <v>134.6</v>
+      </c>
+      <c r="F468" t="n">
+        <v>151.3</v>
+      </c>
+      <c r="G468" t="n">
+        <v>12.4</v>
+      </c>
+      <c r="H468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I468" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>河南区</t>
+        </is>
+      </c>
+      <c r="D469" t="inlineStr">
+        <is>
+          <t>商丘</t>
+        </is>
+      </c>
+      <c r="E469" t="n">
+        <v>115.3</v>
+      </c>
+      <c r="F469" t="n">
+        <v>128</v>
+      </c>
+      <c r="G469" t="n">
+        <v>11</v>
+      </c>
+      <c r="H469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I469" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>山西区</t>
+        </is>
+      </c>
+      <c r="D470" t="inlineStr">
+        <is>
+          <t>长治</t>
+        </is>
+      </c>
+      <c r="E470" t="n">
+        <v>93.59999999999999</v>
+      </c>
+      <c r="F470" t="n">
+        <v>103.6</v>
+      </c>
+      <c r="G470" t="n">
+        <v>10.6</v>
+      </c>
+      <c r="H470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I470" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D471" t="inlineStr">
+        <is>
+          <t>南通</t>
+        </is>
+      </c>
+      <c r="E471" t="n">
+        <v>198.6</v>
+      </c>
+      <c r="F471" t="n">
+        <v>218.6</v>
+      </c>
+      <c r="G471" t="n">
+        <v>10.1</v>
+      </c>
+      <c r="H471" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="I471" t="n">
+        <v>38.2</v>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>粤东区</t>
+        </is>
+      </c>
+      <c r="D472" t="inlineStr">
+        <is>
+          <t>揭阳</t>
+        </is>
+      </c>
+      <c r="E472" t="n">
+        <v>216.6</v>
+      </c>
+      <c r="F472" t="n">
+        <v>234.1</v>
+      </c>
+      <c r="G472" t="n">
+        <v>8</v>
+      </c>
+      <c r="H472" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="I472" t="n">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D473" t="inlineStr">
+        <is>
+          <t>菏泽</t>
+        </is>
+      </c>
+      <c r="E473" t="n">
+        <v>168.1</v>
+      </c>
+      <c r="F473" t="n">
+        <v>177</v>
+      </c>
+      <c r="G473" t="n">
+        <v>5.3</v>
+      </c>
+      <c r="H473" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="I473" t="n">
+        <v>11.9</v>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>山东区</t>
+        </is>
+      </c>
+      <c r="D474" t="inlineStr">
+        <is>
+          <t>临沂</t>
+        </is>
+      </c>
+      <c r="E474" t="n">
+        <v>220.3</v>
+      </c>
+      <c r="F474" t="n">
+        <v>230.7</v>
+      </c>
+      <c r="G474" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="H474" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="I474" t="n">
+        <v>45.8</v>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D475" t="inlineStr">
+        <is>
+          <t>深圳</t>
+        </is>
+      </c>
+      <c r="E475" t="n">
+        <v>173.6</v>
+      </c>
+      <c r="F475" t="n">
+        <v>175.8</v>
+      </c>
+      <c r="G475" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="H475" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="I475" t="n">
+        <v>11.2</v>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>安徽区</t>
+        </is>
+      </c>
+      <c r="D476" t="inlineStr">
+        <is>
+          <t>合肥</t>
+        </is>
+      </c>
+      <c r="E476" t="n">
+        <v>176.6</v>
+      </c>
+      <c r="F476" t="n">
+        <v>177.9</v>
+      </c>
+      <c r="G476" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="H476" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="I476" t="n">
+        <v>12.5</v>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>江苏区</t>
+        </is>
+      </c>
+      <c r="D477" t="inlineStr">
+        <is>
+          <t>淮安</t>
+        </is>
+      </c>
+      <c r="E477" t="n">
+        <v>209.5</v>
+      </c>
+      <c r="F477" t="n">
+        <v>209.2</v>
+      </c>
+      <c r="G477" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="H477" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="I477" t="n">
+        <v>32.3</v>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>广东区</t>
+        </is>
+      </c>
+      <c r="D478" t="inlineStr">
+        <is>
+          <t>广州</t>
+        </is>
+      </c>
+      <c r="E478" t="n">
+        <v>180</v>
+      </c>
+      <c r="F478" t="n">
+        <v>176.4</v>
+      </c>
+      <c r="G478" t="n">
+        <v>-1.9</v>
+      </c>
+      <c r="H478" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="I478" t="n">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>贵州区</t>
+        </is>
+      </c>
+      <c r="D479" t="inlineStr">
+        <is>
+          <t>贵阳</t>
+        </is>
+      </c>
+      <c r="E479" t="n">
+        <v>184.1</v>
+      </c>
+      <c r="F479" t="n">
+        <v>176.5</v>
+      </c>
+      <c r="G479" t="n">
+        <v>-4.1</v>
+      </c>
+      <c r="H479" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="I479" t="n">
+        <v>11.6</v>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>卸车岗</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>浙北区</t>
+        </is>
+      </c>
+      <c r="D480" t="inlineStr">
+        <is>
+          <t>杭州</t>
+        </is>
+      </c>
+      <c r="E480" t="n">
+        <v>220.1</v>
+      </c>
+      <c r="F480" t="n">
+        <v>207.1</v>
+      </c>
+      <c r="G480" t="n">
+        <v>-5.9</v>
+      </c>
+      <c r="H480" t="n">
+        <v>158.1</v>
+      </c>
+      <c r="I480" t="n">
+        <v>30.9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
